--- a/Sales Analytics Dashboard - FINAL.xlsx
+++ b/Sales Analytics Dashboard - FINAL.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7a7909b60f4dae64/Desktop/SALES ANALYTICS DASHBOARD 010101/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7a7909b60f4dae64/Desktop/0101/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8BE9D854-D624-48C0-A998-5621ABB972AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{179AD205-EF86-454D-9AFC-47EF06E3CAC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4657" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4658" uniqueCount="171">
   <si>
     <t>HELPERS</t>
   </si>
@@ -1794,88 +1794,18 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="17" fillId="7" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="7" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="24" fillId="7" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="7" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="7" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="27" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="29" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="30" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="31" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="31" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1908,10 +1838,6 @@
     <xf numFmtId="3" fontId="6" fillId="12" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="32" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="33" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="34" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -1950,41 +1876,44 @@
     <xf numFmtId="0" fontId="15" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="36" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="21" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="37" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="38" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="42" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="39" fillId="14" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="40" fillId="14" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="40" fillId="14" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="41" fillId="14" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="14" borderId="41" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="14" borderId="47" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="14" borderId="43" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1995,28 +1924,53 @@
     <xf numFmtId="0" fontId="26" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="38" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="24" fillId="7" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="39" fillId="14" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="30" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="14" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="30" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="14" borderId="41" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="14" borderId="43" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="36" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="7" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="23" fillId="11" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2029,6 +1983,9 @@
     <xf numFmtId="0" fontId="23" fillId="11" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="11" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2038,13 +1995,11 @@
     <xf numFmtId="0" fontId="23" fillId="11" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="14" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="41" fillId="14" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="14" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="41" fillId="14" borderId="47" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="10" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2064,6 +2019,51 @@
     <xf numFmtId="0" fontId="43" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="7" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="7" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="7" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="14" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2518,10 +2518,10 @@
   <colors>
     <mruColors>
       <color rgb="FF0E7490"/>
+      <color rgb="FF162C4C"/>
       <color rgb="FF081322"/>
       <color rgb="FF0F2038"/>
       <color rgb="FF1C3A63"/>
-      <color rgb="FF162C4C"/>
     </mruColors>
   </colors>
   <extLst>
@@ -2597,32 +2597,6 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="lt1">
-                  <a:lumMod val="95000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:effectLst>
-                <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
-                  <a:prstClr val="black">
-                    <a:alpha val="40000"/>
-                  </a:prstClr>
-                </a:outerShdw>
-              </a:effectLst>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -2692,6 +2666,9 @@
                 <c:pt idx="0">
                   <c:v>Jan</c:v>
                 </c:pt>
+                <c:pt idx="1">
+                  <c:v>Feb</c:v>
+                </c:pt>
                 <c:pt idx="2">
                   <c:v>Mar</c:v>
                 </c:pt>
@@ -2732,40 +2709,40 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>798620.35000000009</c:v>
+                  <c:v>504544.72999999992</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>384847.49</c:v>
+                  <c:v>60199.479999999996</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>75262.539999999994</c:v>
+                  <c:v>53806.63</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>431756.67000000004</c:v>
+                  <c:v>490493.69000000006</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>208424.18</c:v>
+                  <c:v>220014.36000000004</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>270459.49</c:v>
+                  <c:v>321726.38</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>490806.39999999997</c:v>
+                  <c:v>218639.71</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>383846.58999999997</c:v>
+                  <c:v>321530.51</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>472693.69</c:v>
+                  <c:v>267610.3899999999</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>156417.44000000003</c:v>
+                  <c:v>98548.020000000019</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>309229.51999999996</c:v>
+                  <c:v>405598.20999999996</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>931831.9500000003</c:v>
+                  <c:v>341333.08</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2820,38 +2797,41 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>5286472.3040000005</c:v>
+                </c:pt>
                 <c:pt idx="1">
-                  <c:v>4914196.3100000005</c:v>
+                  <c:v>5286472.3040000005</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4914196.3100000005</c:v>
+                  <c:v>5286472.3040000005</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4914196.3100000005</c:v>
+                  <c:v>5286472.3040000005</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4914196.3100000005</c:v>
+                  <c:v>5286472.3040000005</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4914196.3100000005</c:v>
+                  <c:v>5286472.3040000005</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4914196.3100000005</c:v>
+                  <c:v>5286472.3040000005</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4914196.3100000005</c:v>
+                  <c:v>5286472.3040000005</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>4914196.3100000005</c:v>
+                  <c:v>5286472.3040000005</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>4914196.3100000005</c:v>
+                  <c:v>5286472.3040000005</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>4914196.3100000005</c:v>
+                  <c:v>5286472.3040000005</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>4914196.3100000005</c:v>
+                  <c:v>5286472.3040000005</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3051,11 +3031,12 @@
   <c:spPr>
     <a:gradFill flip="none" rotWithShape="1">
       <a:gsLst>
-        <a:gs pos="0">
-          <a:schemeClr val="dk1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
+        <a:gs pos="10000">
+          <a:srgbClr val="002060">
+            <a:lumMod val="94000"/>
+            <a:lumOff val="6000"/>
+            <a:alpha val="56000"/>
+          </a:srgbClr>
         </a:gs>
         <a:gs pos="100000">
           <a:schemeClr val="dk1">
@@ -3072,7 +3053,13 @@
     <a:ln>
       <a:noFill/>
     </a:ln>
-    <a:effectLst/>
+    <a:effectLst>
+      <a:glow rad="139700">
+        <a:srgbClr val="00B0F0">
+          <a:alpha val="78000"/>
+        </a:srgbClr>
+      </a:glow>
+    </a:effectLst>
   </c:spPr>
   <c:txPr>
     <a:bodyPr/>
@@ -3161,32 +3148,6 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="lt1">
-                  <a:lumMod val="95000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:effectLst>
-                <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
-                  <a:prstClr val="black">
-                    <a:alpha val="40000"/>
-                  </a:prstClr>
-                </a:outerShdw>
-              </a:effectLst>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -3243,6 +3204,9 @@
                 <c:pt idx="0">
                   <c:v>Jan</c:v>
                 </c:pt>
+                <c:pt idx="1">
+                  <c:v>Feb</c:v>
+                </c:pt>
                 <c:pt idx="2">
                   <c:v>Mar</c:v>
                 </c:pt>
@@ -3283,40 +3247,40 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>798620.35000000009</c:v>
+                  <c:v>504544.72999999992</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>384847.49</c:v>
+                  <c:v>60199.479999999996</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>75262.539999999994</c:v>
+                  <c:v>53806.63</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>431756.67000000004</c:v>
+                  <c:v>490493.69000000006</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>208424.18</c:v>
+                  <c:v>220014.36000000004</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>270459.49</c:v>
+                  <c:v>321726.38</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>490806.39999999997</c:v>
+                  <c:v>218639.71</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>383846.58999999997</c:v>
+                  <c:v>321530.51</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>472693.69</c:v>
+                  <c:v>267610.3899999999</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>156417.44000000003</c:v>
+                  <c:v>98548.020000000019</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>309229.51999999996</c:v>
+                  <c:v>405598.20999999996</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>931831.9500000003</c:v>
+                  <c:v>341333.08</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3381,40 +3345,40 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>303475.74</c:v>
+                  <c:v>191727</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>146242.03999999998</c:v>
+                  <c:v>22875.79</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>28599.760000000002</c:v>
+                  <c:v>20446.52</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>164067.55000000002</c:v>
+                  <c:v>186387.59</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>79201.190000000017</c:v>
+                  <c:v>83605.440000000002</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>102774.62</c:v>
+                  <c:v>122256.01000000001</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>186506.44</c:v>
+                  <c:v>83083.09</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>145861.68999999997</c:v>
+                  <c:v>122181.61</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>179623.61000000002</c:v>
+                  <c:v>101691.93000000001</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>59438.630000000005</c:v>
+                  <c:v>37448.239999999998</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>117507.21000000002</c:v>
+                  <c:v>154127.32</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>354096.13999999996</c:v>
+                  <c:v>129706.55</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3644,13 +3608,19 @@
   <c:spPr>
     <a:gradFill flip="none" rotWithShape="1">
       <a:gsLst>
-        <a:gs pos="0">
+        <a:gs pos="97279">
           <a:schemeClr val="dk1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="85000"/>
+            <a:lumOff val="15000"/>
           </a:schemeClr>
         </a:gs>
-        <a:gs pos="100000">
+        <a:gs pos="33000">
+          <a:srgbClr val="002060">
+            <a:lumMod val="95000"/>
+            <a:lumOff val="5000"/>
+          </a:srgbClr>
+        </a:gs>
+        <a:gs pos="94000">
           <a:schemeClr val="dk1">
             <a:lumMod val="85000"/>
             <a:lumOff val="15000"/>
@@ -3665,7 +3635,13 @@
     <a:ln>
       <a:noFill/>
     </a:ln>
-    <a:effectLst/>
+    <a:effectLst>
+      <a:glow rad="139700">
+        <a:srgbClr val="00B0F0">
+          <a:alpha val="90000"/>
+        </a:srgbClr>
+      </a:glow>
+    </a:effectLst>
   </c:spPr>
   <c:txPr>
     <a:bodyPr/>
@@ -3921,10 +3897,10 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>2024</c:v>
+                  <c:v>2023</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2023</c:v>
+                  <c:v>2022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3936,10 +3912,10 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>4914196.3100000015</c:v>
+                  <c:v>3304045.1900000009</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3304045.1900000009</c:v>
+                  <c:v>2945037.5700000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4083,11 +4059,12 @@
   <c:spPr>
     <a:gradFill flip="none" rotWithShape="1">
       <a:gsLst>
-        <a:gs pos="0">
-          <a:schemeClr val="dk1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
+        <a:gs pos="6000">
+          <a:srgbClr val="002060">
+            <a:lumMod val="89000"/>
+            <a:lumOff val="11000"/>
+            <a:alpha val="91000"/>
+          </a:srgbClr>
         </a:gs>
         <a:gs pos="100000">
           <a:schemeClr val="dk1">
@@ -4104,7 +4081,11 @@
     <a:ln>
       <a:noFill/>
     </a:ln>
-    <a:effectLst/>
+    <a:effectLst>
+      <a:glow rad="139700">
+        <a:srgbClr val="00B0F0"/>
+      </a:glow>
+    </a:effectLst>
   </c:spPr>
   <c:txPr>
     <a:bodyPr/>
@@ -4245,6 +4226,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-BB15-4A6A-A529-6FB678D84C37}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -4275,6 +4261,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-BB15-4A6A-A529-6FB678D84C37}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -4305,6 +4296,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-BB15-4A6A-A529-6FB678D84C37}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -4335,6 +4331,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-BB15-4A6A-A529-6FB678D84C37}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
@@ -4365,6 +4366,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-BB15-4A6A-A529-6FB678D84C37}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="5"/>
@@ -4395,6 +4401,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-BB15-4A6A-A529-6FB678D84C37}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="6"/>
@@ -4428,6 +4439,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000D-BB15-4A6A-A529-6FB678D84C37}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="7"/>
@@ -4461,6 +4477,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000F-BB15-4A6A-A529-6FB678D84C37}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="8"/>
@@ -4494,6 +4515,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000011-BB15-4A6A-A529-6FB678D84C37}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="9"/>
@@ -4527,6 +4553,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000013-BB15-4A6A-A529-6FB678D84C37}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strRef>
@@ -4534,34 +4565,34 @@
               <c:strCache>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
+                  <c:v>Laptop</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Floor Lamp</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Smartphone</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Monitor</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Desk</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>Headset</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="6">
                   <c:v>Sofa</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>Desk</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Smartphone</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Monitor</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Bookshelf</c:v>
-                </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>Tablet</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Laptop</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>Office Chair</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>Floor Lamp</c:v>
+                  <c:v>Sweater</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4573,34 +4604,34 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>759688.02</c:v>
+                  <c:v>556108.1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>691271.67</c:v>
+                  <c:v>477858.96</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>548078.28</c:v>
+                  <c:v>381998.4</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>471256.17000000004</c:v>
+                  <c:v>298699.01</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>435057.76999999996</c:v>
+                  <c:v>294378.95</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>425258.29000000004</c:v>
+                  <c:v>281950.75</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>411205.34</c:v>
+                  <c:v>212310.41999999998</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>360465.91999999998</c:v>
+                  <c:v>210989.74</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>216559.27999999997</c:v>
+                  <c:v>169379.5</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>123282.81</c:v>
+                  <c:v>68513.939999999988</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4744,11 +4775,17 @@
   <c:spPr>
     <a:gradFill flip="none" rotWithShape="1">
       <a:gsLst>
-        <a:gs pos="0">
+        <a:gs pos="97279">
           <a:schemeClr val="dk1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="85000"/>
+            <a:lumOff val="15000"/>
           </a:schemeClr>
+        </a:gs>
+        <a:gs pos="21000">
+          <a:srgbClr val="002060">
+            <a:lumMod val="92000"/>
+            <a:lumOff val="8000"/>
+          </a:srgbClr>
         </a:gs>
         <a:gs pos="100000">
           <a:schemeClr val="dk1">
@@ -4765,7 +4802,13 @@
     <a:ln>
       <a:noFill/>
     </a:ln>
-    <a:effectLst/>
+    <a:effectLst>
+      <a:glow rad="139700">
+        <a:srgbClr val="00B0F0">
+          <a:alpha val="86000"/>
+        </a:srgbClr>
+      </a:glow>
+    </a:effectLst>
   </c:spPr>
   <c:txPr>
     <a:bodyPr/>
@@ -5246,19 +5289,19 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>83951.659999999974</c:v>
+                  <c:v>47001.42000000002</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2004450.33</c:v>
+                  <c:v>1213707.4200000002</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>216590.40999999997</c:v>
+                  <c:v>183824.42</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>171530.68999999994</c:v>
+                  <c:v>129765.93000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2437673.2199999997</c:v>
+                  <c:v>1729746.0000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5326,11 +5369,11 @@
   <c:spPr>
     <a:gradFill flip="none" rotWithShape="1">
       <a:gsLst>
-        <a:gs pos="0">
-          <a:schemeClr val="dk1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
+        <a:gs pos="43000">
+          <a:srgbClr val="002060">
+            <a:lumMod val="93000"/>
+            <a:lumOff val="7000"/>
+          </a:srgbClr>
         </a:gs>
         <a:gs pos="100000">
           <a:schemeClr val="dk1">
@@ -5345,9 +5388,19 @@
       <a:tileRect/>
     </a:gradFill>
     <a:ln>
-      <a:noFill/>
+      <a:solidFill>
+        <a:schemeClr val="accent1">
+          <a:alpha val="64000"/>
+        </a:schemeClr>
+      </a:solidFill>
     </a:ln>
-    <a:effectLst/>
+    <a:effectLst>
+      <a:glow rad="139700">
+        <a:srgbClr val="00B0F0">
+          <a:alpha val="90000"/>
+        </a:srgbClr>
+      </a:glow>
+    </a:effectLst>
   </c:spPr>
   <c:txPr>
     <a:bodyPr/>
@@ -5498,6 +5551,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-2E1B-4191-BF5A-8BA6F558D2A6}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -5528,6 +5586,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-2E1B-4191-BF5A-8BA6F558D2A6}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -5558,6 +5621,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-2E1B-4191-BF5A-8BA6F558D2A6}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -5588,6 +5656,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-2E1B-4191-BF5A-8BA6F558D2A6}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
@@ -5618,6 +5691,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-2E1B-4191-BF5A-8BA6F558D2A6}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strRef>
@@ -5649,19 +5727,19 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>644006.04000000015</c:v>
+                  <c:v>1091350.9099999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1432864.93</c:v>
+                  <c:v>576134.40999999992</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>837545.24</c:v>
+                  <c:v>542262.50999999978</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1083542.3099999998</c:v>
+                  <c:v>610033.9</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>916237.7899999998</c:v>
+                  <c:v>484263.4599999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5805,11 +5883,18 @@
   <c:spPr>
     <a:gradFill flip="none" rotWithShape="1">
       <a:gsLst>
-        <a:gs pos="0">
+        <a:gs pos="97279">
           <a:schemeClr val="dk1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="85000"/>
+            <a:lumOff val="15000"/>
           </a:schemeClr>
+        </a:gs>
+        <a:gs pos="9000">
+          <a:srgbClr val="002060">
+            <a:alpha val="38000"/>
+            <a:lumMod val="77000"/>
+            <a:lumOff val="23000"/>
+          </a:srgbClr>
         </a:gs>
         <a:gs pos="100000">
           <a:schemeClr val="dk1">
@@ -5824,9 +5909,20 @@
       <a:tileRect/>
     </a:gradFill>
     <a:ln>
-      <a:noFill/>
+      <a:solidFill>
+        <a:srgbClr val="002060"/>
+      </a:solidFill>
     </a:ln>
-    <a:effectLst/>
+    <a:effectLst>
+      <a:glow rad="139700">
+        <a:srgbClr val="00B0F0">
+          <a:alpha val="79000"/>
+        </a:srgbClr>
+      </a:glow>
+      <a:outerShdw blurRad="50800" dist="50800" dir="5400000" algn="ctr" rotWithShape="0">
+        <a:srgbClr val="002060"/>
+      </a:outerShdw>
+    </a:effectLst>
   </c:spPr>
   <c:txPr>
     <a:bodyPr/>
@@ -5985,6 +6081,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-B813-4776-B582-A349FE44E313}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -6015,6 +6116,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-B813-4776-B582-A349FE44E313}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -6045,6 +6151,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-B813-4776-B582-A349FE44E313}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -6078,6 +6189,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-B813-4776-B582-A349FE44E313}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
@@ -6111,6 +6227,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-B813-4776-B582-A349FE44E313}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="5"/>
@@ -6144,6 +6265,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-B813-4776-B582-A349FE44E313}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strRef>
@@ -6178,22 +6304,22 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>873158.79</c:v>
+                  <c:v>539907.66999999993</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>677603.15000000014</c:v>
+                  <c:v>517561.36</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>635295.81000000006</c:v>
+                  <c:v>559937.65999999992</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>631248.94999999995</c:v>
+                  <c:v>441005.19999999984</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>761218.98</c:v>
+                  <c:v>747025.21</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1335670.6299999999</c:v>
+                  <c:v>498608.08999999991</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6278,10 +6404,9 @@
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="lt1">
-                  <a:lumMod val="95000"/>
+                <a:srgbClr val="002060">
                   <a:alpha val="10000"/>
-                </a:schemeClr>
+                </a:srgbClr>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -6337,11 +6462,18 @@
   <c:spPr>
     <a:gradFill flip="none" rotWithShape="1">
       <a:gsLst>
-        <a:gs pos="0">
+        <a:gs pos="97279">
           <a:schemeClr val="dk1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="85000"/>
+            <a:lumOff val="15000"/>
           </a:schemeClr>
+        </a:gs>
+        <a:gs pos="11000">
+          <a:srgbClr val="002060">
+            <a:alpha val="65000"/>
+            <a:lumMod val="83000"/>
+            <a:lumOff val="17000"/>
+          </a:srgbClr>
         </a:gs>
         <a:gs pos="100000">
           <a:schemeClr val="dk1">
@@ -6358,7 +6490,11 @@
     <a:ln>
       <a:noFill/>
     </a:ln>
-    <a:effectLst/>
+    <a:effectLst>
+      <a:glow rad="127000">
+        <a:srgbClr val="00B0F0"/>
+      </a:glow>
+    </a:effectLst>
   </c:spPr>
   <c:txPr>
     <a:bodyPr/>
@@ -6379,8 +6515,42 @@
 </file>
 
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="18">
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
   <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
 </cs:colorStyle>
 </file>
 
@@ -6505,86 +6675,6 @@
 </file>
 
 <file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="11">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent3"/>
@@ -6622,1032 +6712,6 @@
 </file>
 
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="328">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:gradFill flip="none" rotWithShape="1">
-        <a:gsLst>
-          <a:gs pos="0">
-            <a:schemeClr val="dk1">
-              <a:lumMod val="65000"/>
-              <a:lumOff val="35000"/>
-            </a:schemeClr>
-          </a:gs>
-          <a:gs pos="100000">
-            <a:schemeClr val="dk1">
-              <a:lumMod val="85000"/>
-              <a:lumOff val="15000"/>
-            </a:schemeClr>
-          </a:gs>
-        </a:gsLst>
-        <a:path path="circle">
-          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-        </a:path>
-        <a:tileRect/>
-      </a:gradFill>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="34925" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:gradFill>
-        <a:gsLst>
-          <a:gs pos="100000">
-            <a:schemeClr val="dk1">
-              <a:lumMod val="95000"/>
-              <a:lumOff val="5000"/>
-            </a:schemeClr>
-          </a:gs>
-          <a:gs pos="0">
-            <a:schemeClr val="dk1">
-              <a:lumMod val="75000"/>
-              <a:lumOff val="25000"/>
-            </a:schemeClr>
-          </a:gs>
-        </a:gsLst>
-        <a:path path="circle">
-          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-        </a:path>
-      </a:gradFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="10000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="5000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="95000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1600" b="1" kern="1200" spc="100" baseline="0">
-      <a:effectLst>
-        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
-          <a:prstClr val="black">
-            <a:alpha val="40000"/>
-          </a:prstClr>
-        </a:outerShdw>
-      </a:effectLst>
-    </cs:defRPr>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:gradFill>
-        <a:gsLst>
-          <a:gs pos="100000">
-            <a:schemeClr val="lt1">
-              <a:lumMod val="85000"/>
-            </a:schemeClr>
-          </a:gs>
-          <a:gs pos="0">
-            <a:schemeClr val="lt1"/>
-          </a:gs>
-        </a:gsLst>
-        <a:path path="circle">
-          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-        </a:path>
-      </a:gradFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="328">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:gradFill flip="none" rotWithShape="1">
-        <a:gsLst>
-          <a:gs pos="0">
-            <a:schemeClr val="dk1">
-              <a:lumMod val="65000"/>
-              <a:lumOff val="35000"/>
-            </a:schemeClr>
-          </a:gs>
-          <a:gs pos="100000">
-            <a:schemeClr val="dk1">
-              <a:lumMod val="85000"/>
-              <a:lumOff val="15000"/>
-            </a:schemeClr>
-          </a:gs>
-        </a:gsLst>
-        <a:path path="circle">
-          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-        </a:path>
-        <a:tileRect/>
-      </a:gradFill>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="34925" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:gradFill>
-        <a:gsLst>
-          <a:gs pos="100000">
-            <a:schemeClr val="dk1">
-              <a:lumMod val="95000"/>
-              <a:lumOff val="5000"/>
-            </a:schemeClr>
-          </a:gs>
-          <a:gs pos="0">
-            <a:schemeClr val="dk1">
-              <a:lumMod val="75000"/>
-              <a:lumOff val="25000"/>
-            </a:schemeClr>
-          </a:gs>
-        </a:gsLst>
-        <a:path path="circle">
-          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-        </a:path>
-      </a:gradFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="10000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="5000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="95000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1600" b="1" kern="1200" spc="100" baseline="0">
-      <a:effectLst>
-        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
-          <a:prstClr val="black">
-            <a:alpha val="40000"/>
-          </a:prstClr>
-        </a:outerShdw>
-      </a:effectLst>
-    </cs:defRPr>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:gradFill>
-        <a:gsLst>
-          <a:gs pos="100000">
-            <a:schemeClr val="lt1">
-              <a:lumMod val="85000"/>
-            </a:schemeClr>
-          </a:gs>
-          <a:gs pos="0">
-            <a:schemeClr val="lt1"/>
-          </a:gs>
-        </a:gsLst>
-        <a:path path="circle">
-          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-        </a:path>
-      </a:gradFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="209">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -8138,6 +7202,998 @@
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="209">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="85000"/>
+              <a:lumOff val="15000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="5000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" spc="100" baseline="0">
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:defRPr>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="257">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="85000"/>
+              <a:lumOff val="15000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="5000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" spc="100" baseline="0">
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:defRPr>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
@@ -8640,998 +8696,6 @@
 </file>
 
 <file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="257">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:gradFill flip="none" rotWithShape="1">
-        <a:gsLst>
-          <a:gs pos="0">
-            <a:schemeClr val="dk1">
-              <a:lumMod val="65000"/>
-              <a:lumOff val="35000"/>
-            </a:schemeClr>
-          </a:gs>
-          <a:gs pos="100000">
-            <a:schemeClr val="dk1">
-              <a:lumMod val="85000"/>
-              <a:lumOff val="15000"/>
-            </a:schemeClr>
-          </a:gs>
-        </a:gsLst>
-        <a:path path="circle">
-          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-        </a:path>
-        <a:tileRect/>
-      </a:gradFill>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="34925" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:prstDash val="dash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="10000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="5000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:prstDash val="dash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="95000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1600" b="1" kern="1200" spc="100" baseline="0">
-      <a:effectLst>
-        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
-          <a:prstClr val="black">
-            <a:alpha val="40000"/>
-          </a:prstClr>
-        </a:outerShdw>
-      </a:effectLst>
-    </cs:defRPr>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="209">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:gradFill flip="none" rotWithShape="1">
-        <a:gsLst>
-          <a:gs pos="0">
-            <a:schemeClr val="dk1">
-              <a:lumMod val="65000"/>
-              <a:lumOff val="35000"/>
-            </a:schemeClr>
-          </a:gs>
-          <a:gs pos="100000">
-            <a:schemeClr val="dk1">
-              <a:lumMod val="85000"/>
-              <a:lumOff val="15000"/>
-            </a:schemeClr>
-          </a:gs>
-        </a:gsLst>
-        <a:path path="circle">
-          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-        </a:path>
-        <a:tileRect/>
-      </a:gradFill>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="34925" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:prstDash val="dash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="10000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="5000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:prstDash val="dash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="95000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1600" b="1" kern="1200" spc="100" baseline="0">
-      <a:effectLst>
-        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
-          <a:prstClr val="black">
-            <a:alpha val="40000"/>
-          </a:prstClr>
-        </a:outerShdw>
-      </a:effectLst>
-    </cs:defRPr>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="209">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -10131,12 +9195,12 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>60960</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>284480</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1311104</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>245806</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="6268720" cy="3043409"/>
+    <xdr:ext cx="7632096" cy="3729017"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
@@ -10163,11 +9227,11 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>122903</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>17661</xdr:rowOff>
+      <xdr:rowOff>211185</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="4886960" cy="2644259"/>
+    <xdr:ext cx="5616678" cy="3389880"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="3" name="Chart 2">
@@ -10194,11 +9258,11 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>406400</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>436880</xdr:rowOff>
+      <xdr:colOff>135192</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>194644</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="4013200" cy="2682240"/>
+    <xdr:ext cx="5013303" cy="3357260"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="4" name="Chart 3">
@@ -10224,12 +9288,12 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>812800</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>287722</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>1212119</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>258096</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="7000240" cy="3065078"/>
+    <xdr:ext cx="8006564" cy="3689352"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="5" name="Chart 4">
@@ -10255,12 +9319,12 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>202447</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>467032</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>26036</xdr:rowOff>
+      <xdr:rowOff>182299</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="4928424" cy="2646044"/>
+    <xdr:ext cx="5300896" cy="3406476"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="6" name="Chart 5">
@@ -10287,11 +9351,11 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>277680</xdr:rowOff>
+      <xdr:colOff>109637</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>243704</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="5506720" cy="3075120"/>
+    <xdr:ext cx="6465686" cy="3691466"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="7" name="Chart 6">
@@ -10318,11 +9382,11 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>447165</xdr:colOff>
+      <xdr:colOff>810962</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>20058</xdr:rowOff>
+      <xdr:rowOff>178611</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="4826293" cy="2666999"/>
+    <xdr:ext cx="5788941" cy="3397873"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="8" name="Chart 7">
@@ -10636,13 +9700,14 @@
     <col min="5" max="5" width="12" style="6" customWidth="1"/>
     <col min="6" max="6" width="16.77734375" style="6" customWidth="1"/>
     <col min="7" max="7" width="12" style="6" customWidth="1"/>
-    <col min="8" max="8" width="16.6640625" style="6" customWidth="1"/>
-    <col min="9" max="9" width="12" style="6" customWidth="1"/>
-    <col min="10" max="10" width="16.77734375" style="6" customWidth="1"/>
-    <col min="11" max="11" width="12" style="6" customWidth="1"/>
+    <col min="8" max="8" width="20.88671875" style="6" customWidth="1"/>
+    <col min="9" max="9" width="17" style="6" customWidth="1"/>
+    <col min="10" max="10" width="21.44140625" style="6" customWidth="1"/>
+    <col min="11" max="11" width="17.21875" style="6" customWidth="1"/>
     <col min="12" max="12" width="21.6640625" style="6" customWidth="1"/>
-    <col min="13" max="14" width="12" style="6" customWidth="1"/>
-    <col min="15" max="15" width="8.33203125" style="6" customWidth="1"/>
+    <col min="13" max="13" width="19.109375" style="6" customWidth="1"/>
+    <col min="14" max="14" width="18.44140625" style="6" customWidth="1"/>
+    <col min="15" max="15" width="20" style="6" customWidth="1"/>
     <col min="16" max="16" width="19.88671875" style="6" customWidth="1"/>
     <col min="17" max="17" width="16.109375" style="6" customWidth="1"/>
     <col min="18" max="18" width="21.6640625" style="6" customWidth="1"/>
@@ -10652,40 +9717,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="25.2" customHeight="1" thickBot="1">
-      <c r="A1" s="114" t="s">
+      <c r="A1" s="173" t="s">
         <v>165</v>
       </c>
-      <c r="B1" s="108"/>
-      <c r="C1" s="108"/>
-      <c r="D1" s="108"/>
-      <c r="E1" s="108"/>
-      <c r="F1" s="108"/>
-      <c r="G1" s="108"/>
-      <c r="H1" s="108"/>
-      <c r="I1" s="108"/>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
-      <c r="M1" s="108"/>
-      <c r="N1" s="108"/>
-      <c r="O1" s="108"/>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="108"/>
-      <c r="S1" s="108"/>
-      <c r="T1" s="108"/>
-      <c r="U1" s="108"/>
+      <c r="B1" s="174"/>
+      <c r="C1" s="174"/>
+      <c r="D1" s="174"/>
+      <c r="E1" s="174"/>
+      <c r="F1" s="174"/>
+      <c r="G1" s="174"/>
+      <c r="H1" s="174"/>
+      <c r="I1" s="174"/>
+      <c r="J1" s="174"/>
+      <c r="K1" s="174"/>
+      <c r="L1" s="174"/>
+      <c r="M1" s="174"/>
+      <c r="N1" s="174"/>
+      <c r="O1" s="174"/>
+      <c r="P1" s="174"/>
+      <c r="Q1" s="174"/>
+      <c r="R1" s="174"/>
+      <c r="S1" s="174"/>
+      <c r="T1" s="174"/>
+      <c r="U1" s="174"/>
       <c r="V1" s="7"/>
       <c r="W1" s="7"/>
       <c r="X1" s="7"/>
       <c r="Y1" s="7"/>
       <c r="Z1" s="7"/>
       <c r="AA1" s="7"/>
-      <c r="AB1" s="150" t="s">
+      <c r="AB1" s="122" t="s">
         <v>0</v>
       </c>
-      <c r="AC1" s="150"/>
-      <c r="AD1" s="150"/>
+      <c r="AC1" s="122"/>
+      <c r="AD1" s="122"/>
       <c r="AE1" s="7"/>
       <c r="AF1" s="7"/>
       <c r="AG1" s="7"/>
@@ -10703,62 +9768,62 @@
       <c r="AS1" s="7"/>
     </row>
     <row r="2" spans="1:45" ht="15.6" customHeight="1">
-      <c r="A2" s="106" t="s">
+      <c r="A2" s="155" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="107"/>
-      <c r="C2" s="106" t="s">
+      <c r="B2" s="156"/>
+      <c r="C2" s="155" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="107"/>
-      <c r="E2" s="106" t="s">
+      <c r="D2" s="156"/>
+      <c r="E2" s="155" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="107"/>
-      <c r="G2" s="106" t="s">
+      <c r="F2" s="156"/>
+      <c r="G2" s="155" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="107"/>
-      <c r="I2" s="106" t="s">
+      <c r="H2" s="156"/>
+      <c r="I2" s="155" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="107"/>
-      <c r="K2" s="106" t="s">
+      <c r="J2" s="156"/>
+      <c r="K2" s="155" t="s">
         <v>8</v>
       </c>
-      <c r="L2" s="107"/>
-      <c r="M2" s="106" t="s">
+      <c r="L2" s="156"/>
+      <c r="M2" s="155" t="s">
         <v>9</v>
       </c>
-      <c r="N2" s="109"/>
-      <c r="O2" s="107"/>
+      <c r="N2" s="166"/>
+      <c r="O2" s="156"/>
       <c r="P2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="Q2" s="106" t="s">
+      <c r="Q2" s="155" t="s">
         <v>11</v>
       </c>
-      <c r="R2" s="107"/>
-      <c r="S2" s="106" t="s">
+      <c r="R2" s="156"/>
+      <c r="S2" s="155" t="s">
         <v>12</v>
       </c>
-      <c r="T2" s="107"/>
-      <c r="U2" s="112"/>
+      <c r="T2" s="156"/>
+      <c r="U2" s="102"/>
       <c r="V2" s="7"/>
       <c r="W2" s="7"/>
       <c r="X2" s="7"/>
       <c r="Y2" s="7"/>
       <c r="Z2" s="7"/>
       <c r="AA2" s="7"/>
-      <c r="AB2" s="150">
+      <c r="AB2" s="122">
         <f>IF(Q3="USD",1/18.5,1)</f>
         <v>1</v>
       </c>
-      <c r="AC2" s="150">
+      <c r="AC2" s="122">
         <f>SUM(Calc!$B$42:$B$53)*(1+AB3/100)*AB2</f>
-        <v>7862714.0960000008</v>
-      </c>
-      <c r="AD2" s="150" t="s">
+        <v>5286472.3040000005</v>
+      </c>
+      <c r="AD2" s="122" t="s">
         <v>1</v>
       </c>
       <c r="AE2" s="7"/>
@@ -10778,62 +9843,62 @@
       <c r="AS2" s="7"/>
     </row>
     <row r="3" spans="1:45" ht="29.4" customHeight="1" thickBot="1">
-      <c r="A3" s="105">
-        <v>2024</v>
-      </c>
-      <c r="B3" s="115"/>
-      <c r="C3" s="105" t="s">
+      <c r="A3" s="185">
+        <v>2023</v>
+      </c>
+      <c r="B3" s="186"/>
+      <c r="C3" s="185" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="115"/>
-      <c r="E3" s="105" t="s">
+      <c r="D3" s="186"/>
+      <c r="E3" s="185" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="115"/>
-      <c r="G3" s="105" t="s">
+      <c r="F3" s="186"/>
+      <c r="G3" s="185" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="115"/>
-      <c r="I3" s="185" t="s">
+      <c r="H3" s="186"/>
+      <c r="I3" s="195" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="186"/>
-      <c r="K3" s="105" t="s">
+      <c r="J3" s="196"/>
+      <c r="K3" s="185" t="s">
         <v>14</v>
       </c>
-      <c r="L3" s="115"/>
-      <c r="M3" s="105" t="s">
+      <c r="L3" s="186"/>
+      <c r="M3" s="185" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="116"/>
-      <c r="O3" s="115"/>
+      <c r="N3" s="198"/>
+      <c r="O3" s="186"/>
       <c r="P3" s="10">
         <v>60</v>
       </c>
-      <c r="Q3" s="105" t="s">
+      <c r="Q3" s="185" t="s">
         <v>15</v>
       </c>
-      <c r="R3" s="115"/>
-      <c r="S3" s="105" t="s">
+      <c r="R3" s="186"/>
+      <c r="S3" s="185" t="s">
         <v>16</v>
       </c>
-      <c r="T3" s="115"/>
-      <c r="U3" s="112"/>
+      <c r="T3" s="186"/>
+      <c r="U3" s="102"/>
       <c r="V3" s="7"/>
       <c r="W3" s="7"/>
       <c r="X3" s="7"/>
       <c r="Y3" s="7"/>
       <c r="Z3" s="7"/>
       <c r="AA3" s="7"/>
-      <c r="AB3" s="150">
+      <c r="AB3" s="122">
         <f>P3</f>
         <v>60</v>
       </c>
-      <c r="AC3" s="150">
+      <c r="AC3" s="122">
         <f>IF(AB4=1,AC$2,"")</f>
-        <v>7862714.0960000008</v>
-      </c>
-      <c r="AD3" s="150" t="s">
+        <v>5286472.3040000005</v>
+      </c>
+      <c r="AD3" s="122" t="s">
         <v>2</v>
       </c>
       <c r="AE3" s="7"/>
@@ -10852,191 +9917,191 @@
       <c r="AR3" s="7"/>
       <c r="AS3" s="7"/>
     </row>
-    <row r="4" spans="1:45" s="132" customFormat="1" ht="25.2" customHeight="1" thickBot="1">
-      <c r="A4" s="129" t="str">
+    <row r="4" spans="1:45" s="108" customFormat="1" ht="25.2" customHeight="1" thickBot="1">
+      <c r="A4" s="175" t="str">
         <f>"ACTIVE FILTERS     YEAR = "&amp;A3&amp;"   |   QUARTER = "&amp;C3&amp;"   |   MONTH = "&amp;E3&amp;"   |   REGION = "&amp;G3&amp;"   |   CATEGORY = "&amp;I3&amp;"   |   SALESPERSON = "&amp;K3&amp;"   |   PRODUCT = "&amp;M3&amp;"   |   GROWTH = "&amp;P3&amp;"%   |   CURRENCY = "&amp;Q3&amp;"   |   TARGET = "&amp;S3</f>
-        <v>ACTIVE FILTERS     YEAR = 2024   |   QUARTER = All   |   MONTH = All   |   REGION = All   |   CATEGORY = All   |   SALESPERSON = All   |   PRODUCT = All   |   GROWTH = 60%   |   CURRENCY = EGP   |   TARGET = ON</v>
-      </c>
-      <c r="B4" s="130"/>
-      <c r="C4" s="130"/>
-      <c r="D4" s="130"/>
-      <c r="E4" s="130"/>
-      <c r="F4" s="130"/>
-      <c r="G4" s="130"/>
-      <c r="H4" s="130"/>
-      <c r="I4" s="130"/>
-      <c r="J4" s="130"/>
-      <c r="K4" s="130"/>
-      <c r="L4" s="130"/>
-      <c r="M4" s="130"/>
-      <c r="N4" s="130"/>
-      <c r="O4" s="130"/>
-      <c r="P4" s="130"/>
-      <c r="Q4" s="130"/>
-      <c r="R4" s="130"/>
-      <c r="S4" s="130"/>
-      <c r="T4" s="130"/>
-      <c r="U4" s="130"/>
-      <c r="V4" s="153"/>
-      <c r="W4" s="131"/>
-      <c r="X4" s="131"/>
-      <c r="Y4" s="131"/>
-      <c r="Z4" s="131"/>
-      <c r="AA4" s="131"/>
-      <c r="AB4" s="151">
+        <v>ACTIVE FILTERS     YEAR = 2023   |   QUARTER = All   |   MONTH = All   |   REGION = All   |   CATEGORY = All   |   SALESPERSON = All   |   PRODUCT = All   |   GROWTH = 60%   |   CURRENCY = EGP   |   TARGET = ON</v>
+      </c>
+      <c r="B4" s="176"/>
+      <c r="C4" s="176"/>
+      <c r="D4" s="176"/>
+      <c r="E4" s="176"/>
+      <c r="F4" s="176"/>
+      <c r="G4" s="176"/>
+      <c r="H4" s="176"/>
+      <c r="I4" s="176"/>
+      <c r="J4" s="176"/>
+      <c r="K4" s="176"/>
+      <c r="L4" s="176"/>
+      <c r="M4" s="176"/>
+      <c r="N4" s="176"/>
+      <c r="O4" s="176"/>
+      <c r="P4" s="176"/>
+      <c r="Q4" s="176"/>
+      <c r="R4" s="176"/>
+      <c r="S4" s="176"/>
+      <c r="T4" s="176"/>
+      <c r="U4" s="176"/>
+      <c r="V4" s="125"/>
+      <c r="W4" s="107"/>
+      <c r="X4" s="107"/>
+      <c r="Y4" s="107"/>
+      <c r="Z4" s="107"/>
+      <c r="AA4" s="107"/>
+      <c r="AB4" s="123">
         <f>IF(S3="ON",1,0)</f>
         <v>1</v>
       </c>
-      <c r="AC4" s="151">
+      <c r="AC4" s="123">
         <f>IF(AB4=1,AC$2,"")</f>
-        <v>7862714.0960000008</v>
-      </c>
-      <c r="AD4" s="151" t="s">
+        <v>5286472.3040000005</v>
+      </c>
+      <c r="AD4" s="123" t="s">
         <v>13</v>
       </c>
-      <c r="AE4" s="131"/>
-      <c r="AF4" s="131"/>
-      <c r="AG4" s="131"/>
-      <c r="AH4" s="131"/>
-      <c r="AI4" s="131"/>
-      <c r="AJ4" s="131"/>
-      <c r="AK4" s="131"/>
-      <c r="AL4" s="131"/>
-      <c r="AM4" s="131"/>
-      <c r="AN4" s="131"/>
-      <c r="AO4" s="131"/>
-      <c r="AP4" s="131"/>
-      <c r="AQ4" s="131"/>
-      <c r="AR4" s="131"/>
-      <c r="AS4" s="131"/>
-    </row>
-    <row r="5" spans="1:45" s="138" customFormat="1" ht="19.2" customHeight="1">
-      <c r="A5" s="134" t="str">
+      <c r="AE4" s="107"/>
+      <c r="AF4" s="107"/>
+      <c r="AG4" s="107"/>
+      <c r="AH4" s="107"/>
+      <c r="AI4" s="107"/>
+      <c r="AJ4" s="107"/>
+      <c r="AK4" s="107"/>
+      <c r="AL4" s="107"/>
+      <c r="AM4" s="107"/>
+      <c r="AN4" s="107"/>
+      <c r="AO4" s="107"/>
+      <c r="AP4" s="107"/>
+      <c r="AQ4" s="107"/>
+      <c r="AR4" s="107"/>
+      <c r="AS4" s="107"/>
+    </row>
+    <row r="5" spans="1:45" s="112" customFormat="1" ht="19.2" customHeight="1">
+      <c r="A5" s="162" t="str">
         <f>IF(Q3="USD","TOTAL REVENUE  (USD)","TOTAL REVENUE  (EGP)")</f>
         <v>TOTAL REVENUE  (EGP)</v>
       </c>
-      <c r="B5" s="135"/>
-      <c r="C5" s="134" t="str">
+      <c r="B5" s="170"/>
+      <c r="C5" s="162" t="str">
         <f>"TOTAL ORDERS"</f>
         <v>TOTAL ORDERS</v>
       </c>
-      <c r="D5" s="135"/>
-      <c r="E5" s="134" t="str">
+      <c r="D5" s="170"/>
+      <c r="E5" s="162" t="str">
         <f>"TOTAL UNITS"</f>
         <v>TOTAL UNITS</v>
       </c>
-      <c r="F5" s="135"/>
-      <c r="G5" s="134" t="str">
+      <c r="F5" s="170"/>
+      <c r="G5" s="162" t="str">
         <f>IF(Q3="USD","AVG ORDER VALUE  (USD)","AVG ORDER VALUE  (EGP)")</f>
         <v>AVG ORDER VALUE  (EGP)</v>
       </c>
-      <c r="H5" s="135"/>
-      <c r="I5" s="134" t="str">
+      <c r="H5" s="170"/>
+      <c r="I5" s="162" t="str">
         <f>IF(Q3="USD","TOTAL PROFIT  (USD)","TOTAL PROFIT  (EGP)")</f>
         <v>TOTAL PROFIT  (EGP)</v>
       </c>
-      <c r="J5" s="135"/>
-      <c r="K5" s="134" t="str">
+      <c r="J5" s="170"/>
+      <c r="K5" s="162" t="str">
         <f>"PROFIT MARGIN"</f>
         <v>PROFIT MARGIN</v>
       </c>
-      <c r="L5" s="166"/>
-      <c r="M5" s="193" t="str">
+      <c r="L5" s="163"/>
+      <c r="M5" s="177" t="str">
         <f ca="1">TEXT(NOW(),"HH:MM:SS")&amp;"   UPDATED"</f>
-        <v>04:47:34   UPDATED</v>
-      </c>
-      <c r="N5" s="194"/>
-      <c r="O5" s="194"/>
-      <c r="P5" s="195"/>
-      <c r="Q5" s="204" t="s">
+        <v>16:41:33   UPDATED</v>
+      </c>
+      <c r="N5" s="178"/>
+      <c r="O5" s="178"/>
+      <c r="P5" s="179"/>
+      <c r="Q5" s="187" t="s">
         <v>167</v>
       </c>
-      <c r="R5" s="204"/>
-      <c r="S5" s="204"/>
-      <c r="T5" s="205"/>
-      <c r="U5" s="136"/>
-      <c r="V5" s="137"/>
-      <c r="W5" s="137"/>
-      <c r="X5" s="137"/>
-      <c r="Y5" s="137"/>
-      <c r="Z5" s="137"/>
-      <c r="AA5" s="137"/>
-      <c r="AB5" s="152"/>
-      <c r="AC5" s="152">
+      <c r="R5" s="187"/>
+      <c r="S5" s="187"/>
+      <c r="T5" s="188"/>
+      <c r="U5" s="110"/>
+      <c r="V5" s="111"/>
+      <c r="W5" s="111"/>
+      <c r="X5" s="111"/>
+      <c r="Y5" s="111"/>
+      <c r="Z5" s="111"/>
+      <c r="AA5" s="111"/>
+      <c r="AB5" s="124"/>
+      <c r="AC5" s="124">
         <f>IF(AB4=1,AC$2,"")</f>
-        <v>7862714.0960000008</v>
-      </c>
-      <c r="AD5" s="152" t="s">
+        <v>5286472.3040000005</v>
+      </c>
+      <c r="AD5" s="124" t="s">
         <v>17</v>
       </c>
-      <c r="AE5" s="137"/>
-      <c r="AF5" s="137"/>
-      <c r="AG5" s="137"/>
-      <c r="AH5" s="137"/>
-      <c r="AI5" s="137"/>
-      <c r="AJ5" s="137"/>
-      <c r="AK5" s="137"/>
-      <c r="AL5" s="137"/>
-      <c r="AM5" s="137"/>
-      <c r="AN5" s="137"/>
-      <c r="AO5" s="137"/>
-      <c r="AP5" s="137"/>
-      <c r="AQ5" s="137"/>
-      <c r="AR5" s="137"/>
-      <c r="AS5" s="137"/>
+      <c r="AE5" s="111"/>
+      <c r="AF5" s="111"/>
+      <c r="AG5" s="111"/>
+      <c r="AH5" s="111"/>
+      <c r="AI5" s="111"/>
+      <c r="AJ5" s="111"/>
+      <c r="AK5" s="111"/>
+      <c r="AL5" s="111"/>
+      <c r="AM5" s="111"/>
+      <c r="AN5" s="111"/>
+      <c r="AO5" s="111"/>
+      <c r="AP5" s="111"/>
+      <c r="AQ5" s="111"/>
+      <c r="AR5" s="111"/>
+      <c r="AS5" s="111"/>
     </row>
     <row r="6" spans="1:45" ht="24.6" customHeight="1">
-      <c r="A6" s="102">
+      <c r="A6" s="199">
         <f>SUM(Calc!$B$42:$B$53)*$AB$2</f>
-        <v>4914196.3100000005</v>
-      </c>
-      <c r="B6" s="103"/>
-      <c r="C6" s="102">
+        <v>3304045.19</v>
+      </c>
+      <c r="B6" s="200"/>
+      <c r="C6" s="199">
         <f>SUM(Calc!$C$42:$C$53)</f>
         <v>180</v>
       </c>
-      <c r="D6" s="103"/>
-      <c r="E6" s="102">
+      <c r="D6" s="200"/>
+      <c r="E6" s="199">
         <f>SUM(Calc!$D$42:$D$53)</f>
-        <v>3831</v>
-      </c>
-      <c r="F6" s="103"/>
-      <c r="G6" s="102">
+        <v>2780</v>
+      </c>
+      <c r="F6" s="200"/>
+      <c r="G6" s="199">
         <f>IFERROR(SUM(Calc!$B$42:$B$53)/SUM(Calc!$C$42:$C$53),0)*$AB$2</f>
-        <v>27301.090611111114</v>
-      </c>
-      <c r="H6" s="103"/>
-      <c r="I6" s="102">
+        <v>18355.806611111111</v>
+      </c>
+      <c r="H6" s="200"/>
+      <c r="I6" s="199">
         <f>SUM(Calc!$F$42:$F$53)*$AB$2</f>
-        <v>1867394.6199999999</v>
-      </c>
-      <c r="J6" s="103"/>
-      <c r="K6" s="104">
+        <v>1255537.0900000001</v>
+      </c>
+      <c r="J6" s="200"/>
+      <c r="K6" s="204">
         <f>IFERROR(SUM(Calc!$F$42:$F$53)/SUM(Calc!$B$42:$B$53),0)</f>
-        <v>0.38000000451752397</v>
-      </c>
-      <c r="L6" s="167"/>
-      <c r="M6" s="196"/>
-      <c r="N6" s="113"/>
-      <c r="O6" s="113"/>
-      <c r="P6" s="197"/>
-      <c r="Q6" s="206"/>
-      <c r="R6" s="206"/>
-      <c r="S6" s="206"/>
-      <c r="T6" s="207"/>
-      <c r="U6" s="117"/>
+        <v>0.37999997512140565</v>
+      </c>
+      <c r="L6" s="205"/>
+      <c r="M6" s="180"/>
+      <c r="N6" s="181"/>
+      <c r="O6" s="181"/>
+      <c r="P6" s="182"/>
+      <c r="Q6" s="189"/>
+      <c r="R6" s="189"/>
+      <c r="S6" s="189"/>
+      <c r="T6" s="190"/>
+      <c r="U6" s="103"/>
       <c r="V6" s="7"/>
       <c r="W6" s="7"/>
       <c r="X6" s="7"/>
       <c r="Y6" s="7"/>
       <c r="Z6" s="7"/>
       <c r="AA6" s="7"/>
-      <c r="AB6" s="150"/>
-      <c r="AC6" s="150">
+      <c r="AB6" s="122"/>
+      <c r="AC6" s="122">
         <f>IF(AB4=1,AC$2,"")</f>
-        <v>7862714.0960000008</v>
-      </c>
-      <c r="AD6" s="150" t="s">
+        <v>5286472.3040000005</v>
+      </c>
+      <c r="AD6" s="122" t="s">
         <v>18</v>
       </c>
       <c r="AE6" s="7"/>
@@ -11056,39 +10121,39 @@
       <c r="AS6" s="7"/>
     </row>
     <row r="7" spans="1:45" ht="18" customHeight="1">
-      <c r="A7" s="122" t="str">
+      <c r="A7" s="164" t="str">
         <f>IF(Q3="USD","TOTAL COST  (USD)","TOTAL COST  (EGP)")</f>
         <v>TOTAL COST  (EGP)</v>
       </c>
-      <c r="B7" s="123"/>
-      <c r="C7" s="122" t="s">
+      <c r="B7" s="165"/>
+      <c r="C7" s="164" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="123"/>
-      <c r="E7" s="122" t="s">
+      <c r="D7" s="165"/>
+      <c r="E7" s="164" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="123"/>
-      <c r="G7" s="122" t="s">
+      <c r="F7" s="165"/>
+      <c r="G7" s="164" t="s">
         <v>26</v>
       </c>
-      <c r="H7" s="123"/>
-      <c r="I7" s="122" t="s">
+      <c r="H7" s="165"/>
+      <c r="I7" s="164" t="s">
         <v>27</v>
       </c>
-      <c r="J7" s="123"/>
-      <c r="K7" s="122" t="s">
+      <c r="J7" s="165"/>
+      <c r="K7" s="164" t="s">
         <v>28</v>
       </c>
-      <c r="L7" s="168"/>
-      <c r="M7" s="196"/>
-      <c r="N7" s="113"/>
-      <c r="O7" s="113"/>
-      <c r="P7" s="197"/>
-      <c r="Q7" s="206"/>
-      <c r="R7" s="206"/>
-      <c r="S7" s="206"/>
-      <c r="T7" s="207"/>
+      <c r="L7" s="203"/>
+      <c r="M7" s="180"/>
+      <c r="N7" s="181"/>
+      <c r="O7" s="181"/>
+      <c r="P7" s="182"/>
+      <c r="Q7" s="189"/>
+      <c r="R7" s="189"/>
+      <c r="S7" s="189"/>
+      <c r="T7" s="190"/>
       <c r="U7" s="7"/>
       <c r="V7" s="7"/>
       <c r="W7" s="7"/>
@@ -11096,12 +10161,12 @@
       <c r="Y7" s="7"/>
       <c r="Z7" s="7"/>
       <c r="AA7" s="7"/>
-      <c r="AB7" s="150"/>
-      <c r="AC7" s="150">
+      <c r="AB7" s="122"/>
+      <c r="AC7" s="122">
         <f>IF(AB4=1,AC$2,"")</f>
-        <v>7862714.0960000008</v>
-      </c>
-      <c r="AD7" s="150" t="s">
+        <v>5286472.3040000005</v>
+      </c>
+      <c r="AD7" s="122" t="s">
         <v>19</v>
       </c>
       <c r="AE7" s="7"/>
@@ -11121,46 +10186,46 @@
       <c r="AS7" s="7"/>
     </row>
     <row r="8" spans="1:45" ht="21" customHeight="1">
-      <c r="A8" s="118">
+      <c r="A8" s="160">
         <f>SUM(Calc!$E$42:$E$53)*$AB$2</f>
-        <v>3046801.69</v>
-      </c>
-      <c r="B8" s="119"/>
-      <c r="C8" s="120" t="str">
+        <v>2048508.0999999996</v>
+      </c>
+      <c r="B8" s="172"/>
+      <c r="C8" s="206" t="str">
         <f>INDEX(Dashboard!$AD$2:$AD$13,MATCH(MAX(Calc!$I$42:$I$53),Calc!$I$42:$I$53,0))</f>
-        <v>Dec</v>
-      </c>
-      <c r="D8" s="119"/>
-      <c r="E8" s="118">
+        <v>Jan</v>
+      </c>
+      <c r="D8" s="172"/>
+      <c r="E8" s="160">
         <f>IFERROR(SUM(Calc!$F$42:$F$53)/SUM(Calc!$C$42:$C$53),0)*$AB$2</f>
-        <v>10374.414555555555</v>
-      </c>
-      <c r="F8" s="119"/>
-      <c r="G8" s="121">
+        <v>6975.2060555555563</v>
+      </c>
+      <c r="F8" s="172"/>
+      <c r="G8" s="171">
         <f>Calc!$F$166</f>
-        <v>0.48732720874196039</v>
-      </c>
-      <c r="H8" s="119"/>
-      <c r="I8" s="121">
+        <v>0.12190256031266879</v>
+      </c>
+      <c r="H8" s="172"/>
+      <c r="I8" s="171">
         <f>IFERROR(SUM(Calc!$E$42:$E$53)/SUM(Calc!$B$42:$B$53),0)</f>
-        <v>0.61999999548247586</v>
-      </c>
-      <c r="J8" s="119"/>
-      <c r="K8" s="118">
+        <v>0.62000002487859429</v>
+      </c>
+      <c r="J8" s="172"/>
+      <c r="K8" s="160">
         <f>MAX(Calc!$I$42:$I$53)</f>
-        <v>931831.9500000003</v>
-      </c>
-      <c r="L8" s="169"/>
-      <c r="M8" s="196"/>
-      <c r="N8" s="113"/>
-      <c r="O8" s="113"/>
-      <c r="P8" s="197"/>
-      <c r="Q8" s="206"/>
-      <c r="R8" s="206"/>
-      <c r="S8" s="206"/>
-      <c r="T8" s="207"/>
+        <v>504544.72999999992</v>
+      </c>
+      <c r="L8" s="161"/>
+      <c r="M8" s="180"/>
+      <c r="N8" s="181"/>
+      <c r="O8" s="181"/>
+      <c r="P8" s="182"/>
+      <c r="Q8" s="189"/>
+      <c r="R8" s="189"/>
+      <c r="S8" s="189"/>
+      <c r="T8" s="190"/>
       <c r="U8" s="7"/>
-      <c r="V8" s="124" t="s">
+      <c r="V8" s="104" t="s">
         <v>166</v>
       </c>
       <c r="W8" s="7"/>
@@ -11168,12 +10233,12 @@
       <c r="Y8" s="7"/>
       <c r="Z8" s="7"/>
       <c r="AA8" s="7"/>
-      <c r="AB8" s="150"/>
-      <c r="AC8" s="150">
+      <c r="AB8" s="122"/>
+      <c r="AC8" s="122">
         <f>IF(AB4=1,AC$2,"")</f>
-        <v>7862714.0960000008</v>
-      </c>
-      <c r="AD8" s="150" t="s">
+        <v>5286472.3040000005</v>
+      </c>
+      <c r="AD8" s="122" t="s">
         <v>21</v>
       </c>
       <c r="AE8" s="7"/>
@@ -11192,139 +10257,139 @@
       <c r="AR8" s="7"/>
       <c r="AS8" s="7"/>
     </row>
-    <row r="9" spans="1:45" s="128" customFormat="1" ht="0.6" customHeight="1" thickBot="1">
-      <c r="J9" s="133"/>
-      <c r="K9" s="133"/>
-      <c r="L9" s="183"/>
-      <c r="M9" s="198"/>
-      <c r="N9" s="199"/>
-      <c r="O9" s="113"/>
-      <c r="P9" s="197"/>
-      <c r="Q9" s="206"/>
-      <c r="R9" s="208"/>
-      <c r="S9" s="208"/>
-      <c r="T9" s="209"/>
-      <c r="U9" s="127"/>
-      <c r="V9" s="127"/>
-      <c r="W9" s="127"/>
-      <c r="X9" s="127"/>
-      <c r="Y9" s="127"/>
-      <c r="Z9" s="127"/>
-      <c r="AA9" s="127"/>
-      <c r="AB9" s="184"/>
-      <c r="AC9" s="184">
+    <row r="9" spans="1:45" s="106" customFormat="1" ht="0.6" customHeight="1" thickBot="1">
+      <c r="J9" s="109"/>
+      <c r="K9" s="109"/>
+      <c r="L9" s="144"/>
+      <c r="M9" s="183"/>
+      <c r="N9" s="184"/>
+      <c r="O9" s="181"/>
+      <c r="P9" s="182"/>
+      <c r="Q9" s="189"/>
+      <c r="R9" s="191"/>
+      <c r="S9" s="191"/>
+      <c r="T9" s="192"/>
+      <c r="U9" s="105"/>
+      <c r="V9" s="105"/>
+      <c r="W9" s="105"/>
+      <c r="X9" s="105"/>
+      <c r="Y9" s="105"/>
+      <c r="Z9" s="105"/>
+      <c r="AA9" s="105"/>
+      <c r="AB9" s="145"/>
+      <c r="AC9" s="145">
         <f>IF(AB4=1,AC$2,"")</f>
-        <v>7862714.0960000008</v>
-      </c>
-      <c r="AD9" s="184" t="s">
+        <v>5286472.3040000005</v>
+      </c>
+      <c r="AD9" s="145" t="s">
         <v>22</v>
       </c>
-      <c r="AE9" s="127"/>
-      <c r="AF9" s="127"/>
-      <c r="AG9" s="127"/>
-      <c r="AH9" s="127"/>
-      <c r="AI9" s="127"/>
-      <c r="AJ9" s="127"/>
-      <c r="AK9" s="127"/>
-      <c r="AL9" s="127"/>
-      <c r="AM9" s="127"/>
-      <c r="AN9" s="127"/>
-      <c r="AO9" s="127"/>
-      <c r="AP9" s="127"/>
-      <c r="AQ9" s="127"/>
-      <c r="AR9" s="127"/>
-      <c r="AS9" s="127"/>
-    </row>
-    <row r="10" spans="1:45" s="179" customFormat="1" ht="18" customHeight="1">
-      <c r="A10" s="180" t="s">
+      <c r="AE9" s="105"/>
+      <c r="AF9" s="105"/>
+      <c r="AG9" s="105"/>
+      <c r="AH9" s="105"/>
+      <c r="AI9" s="105"/>
+      <c r="AJ9" s="105"/>
+      <c r="AK9" s="105"/>
+      <c r="AL9" s="105"/>
+      <c r="AM9" s="105"/>
+      <c r="AN9" s="105"/>
+      <c r="AO9" s="105"/>
+      <c r="AP9" s="105"/>
+      <c r="AQ9" s="105"/>
+      <c r="AR9" s="105"/>
+      <c r="AS9" s="105"/>
+    </row>
+    <row r="10" spans="1:45" s="143" customFormat="1" ht="18" customHeight="1">
+      <c r="A10" s="157" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="181"/>
-      <c r="C10" s="182"/>
-      <c r="D10" s="180" t="s">
+      <c r="B10" s="158"/>
+      <c r="C10" s="159"/>
+      <c r="D10" s="157" t="s">
         <v>33</v>
       </c>
-      <c r="E10" s="181"/>
-      <c r="F10" s="182"/>
-      <c r="G10" s="180" t="s">
+      <c r="E10" s="158"/>
+      <c r="F10" s="159"/>
+      <c r="G10" s="157" t="s">
         <v>34</v>
       </c>
-      <c r="H10" s="181"/>
-      <c r="I10" s="182"/>
-      <c r="J10" s="176"/>
-      <c r="K10" s="176"/>
-      <c r="L10" s="176"/>
-      <c r="M10" s="192"/>
-      <c r="N10" s="192"/>
-      <c r="O10" s="200"/>
-      <c r="P10" s="201" t="s">
+      <c r="H10" s="158"/>
+      <c r="I10" s="159"/>
+      <c r="J10" s="140"/>
+      <c r="K10" s="140"/>
+      <c r="L10" s="140"/>
+      <c r="M10" s="148"/>
+      <c r="N10" s="148"/>
+      <c r="O10" s="149"/>
+      <c r="P10" s="151" t="s">
         <v>169</v>
       </c>
-      <c r="Q10" s="190"/>
-      <c r="R10" s="176"/>
-      <c r="S10" s="176"/>
-      <c r="T10" s="176"/>
-      <c r="U10" s="177"/>
-      <c r="V10" s="177"/>
-      <c r="W10" s="177"/>
-      <c r="X10" s="177"/>
-      <c r="Y10" s="177"/>
-      <c r="Z10" s="177"/>
-      <c r="AA10" s="177"/>
-      <c r="AB10" s="178"/>
-      <c r="AC10" s="178">
+      <c r="Q10" s="152"/>
+      <c r="R10" s="140"/>
+      <c r="S10" s="140"/>
+      <c r="T10" s="140"/>
+      <c r="U10" s="141"/>
+      <c r="V10" s="141"/>
+      <c r="W10" s="141"/>
+      <c r="X10" s="141"/>
+      <c r="Y10" s="141"/>
+      <c r="Z10" s="141"/>
+      <c r="AA10" s="141"/>
+      <c r="AB10" s="142"/>
+      <c r="AC10" s="142">
         <f>IF(AB4=1,AC$2,"")</f>
-        <v>7862714.0960000008</v>
-      </c>
-      <c r="AD10" s="178" t="s">
+        <v>5286472.3040000005</v>
+      </c>
+      <c r="AD10" s="142" t="s">
         <v>23</v>
       </c>
-      <c r="AE10" s="177"/>
-      <c r="AF10" s="177"/>
-      <c r="AG10" s="177"/>
-      <c r="AH10" s="177"/>
-      <c r="AI10" s="177"/>
-      <c r="AJ10" s="177"/>
-      <c r="AK10" s="177"/>
-      <c r="AL10" s="177"/>
-      <c r="AM10" s="177"/>
-      <c r="AN10" s="177"/>
-      <c r="AO10" s="177"/>
-      <c r="AP10" s="177"/>
-      <c r="AQ10" s="177"/>
-      <c r="AR10" s="177"/>
-      <c r="AS10" s="177"/>
+      <c r="AE10" s="141"/>
+      <c r="AF10" s="141"/>
+      <c r="AG10" s="141"/>
+      <c r="AH10" s="141"/>
+      <c r="AI10" s="141"/>
+      <c r="AJ10" s="141"/>
+      <c r="AK10" s="141"/>
+      <c r="AL10" s="141"/>
+      <c r="AM10" s="141"/>
+      <c r="AN10" s="141"/>
+      <c r="AO10" s="141"/>
+      <c r="AP10" s="141"/>
+      <c r="AQ10" s="141"/>
+      <c r="AR10" s="141"/>
+      <c r="AS10" s="141"/>
     </row>
     <row r="11" spans="1:45" ht="34.799999999999997" customHeight="1" thickBot="1">
-      <c r="A11" s="172" t="str">
+      <c r="A11" s="197" t="str">
         <f>INDEX(Calc!$A$75:$A$79,MATCH(MAX(Calc!$B$75:$B$79),Calc!$B$75:$B$79,0))</f>
         <v>Electronics</v>
       </c>
-      <c r="B11" s="173"/>
-      <c r="C11" s="174"/>
-      <c r="D11" s="172" t="str">
+      <c r="B11" s="168"/>
+      <c r="C11" s="169"/>
+      <c r="D11" s="197" t="str">
         <f>INDEX(Calc!$A$84:$A$89,MATCH(MAX(Calc!$B$84:$B$89),Calc!$B$84:$B$89,0))</f>
-        <v>Mona Adel</v>
-      </c>
-      <c r="E11" s="173"/>
-      <c r="F11" s="174"/>
-      <c r="G11" s="175">
+        <v>Khaled Youssef</v>
+      </c>
+      <c r="E11" s="168"/>
+      <c r="F11" s="169"/>
+      <c r="G11" s="167">
         <f>(SUM(Calc!$B$42:$B$53))*(1+$P$3/100)*$AB$2</f>
-        <v>7862714.0960000008</v>
-      </c>
-      <c r="H11" s="173"/>
-      <c r="I11" s="174"/>
-      <c r="J11" s="117"/>
-      <c r="K11" s="117"/>
-      <c r="L11" s="117"/>
-      <c r="M11" s="117"/>
-      <c r="N11" s="117"/>
-      <c r="O11" s="202"/>
-      <c r="P11" s="203"/>
-      <c r="Q11" s="191"/>
-      <c r="R11" s="117"/>
-      <c r="S11" s="117"/>
-      <c r="T11" s="117"/>
+        <v>5286472.3040000005</v>
+      </c>
+      <c r="H11" s="168"/>
+      <c r="I11" s="169"/>
+      <c r="J11" s="103"/>
+      <c r="K11" s="103"/>
+      <c r="L11" s="103"/>
+      <c r="M11" s="103"/>
+      <c r="N11" s="103"/>
+      <c r="O11" s="150"/>
+      <c r="P11" s="153"/>
+      <c r="Q11" s="154"/>
+      <c r="R11" s="103"/>
+      <c r="S11" s="103"/>
+      <c r="T11" s="103"/>
       <c r="U11" s="7"/>
       <c r="V11" s="7"/>
       <c r="W11" s="7"/>
@@ -11332,12 +10397,12 @@
       <c r="Y11" s="7"/>
       <c r="Z11" s="7"/>
       <c r="AA11" s="7"/>
-      <c r="AB11" s="150"/>
-      <c r="AC11" s="150">
+      <c r="AB11" s="122"/>
+      <c r="AC11" s="122">
         <f>IF(AB4=1,AC$2,"")</f>
-        <v>7862714.0960000008</v>
-      </c>
-      <c r="AD11" s="150" t="s">
+        <v>5286472.3040000005</v>
+      </c>
+      <c r="AD11" s="122" t="s">
         <v>29</v>
       </c>
       <c r="AE11" s="7"/>
@@ -11357,26 +10422,26 @@
       <c r="AS11" s="7"/>
     </row>
     <row r="12" spans="1:45" ht="48" customHeight="1">
-      <c r="A12" s="117"/>
-      <c r="B12" s="117"/>
-      <c r="C12" s="117"/>
-      <c r="D12" s="117"/>
-      <c r="E12" s="117"/>
-      <c r="F12" s="117"/>
-      <c r="G12" s="117"/>
-      <c r="H12" s="117"/>
-      <c r="I12" s="117"/>
-      <c r="J12" s="117"/>
-      <c r="K12" s="117"/>
-      <c r="L12" s="117"/>
-      <c r="M12" s="117"/>
-      <c r="N12" s="117"/>
-      <c r="O12" s="117"/>
-      <c r="P12" s="117"/>
-      <c r="Q12" s="117"/>
-      <c r="R12" s="117"/>
-      <c r="S12" s="117"/>
-      <c r="T12" s="117"/>
+      <c r="A12" s="103"/>
+      <c r="B12" s="103"/>
+      <c r="C12" s="103"/>
+      <c r="D12" s="103"/>
+      <c r="E12" s="103"/>
+      <c r="F12" s="103"/>
+      <c r="G12" s="103"/>
+      <c r="H12" s="103"/>
+      <c r="I12" s="103"/>
+      <c r="J12" s="103"/>
+      <c r="K12" s="103"/>
+      <c r="L12" s="103"/>
+      <c r="M12" s="103"/>
+      <c r="N12" s="103"/>
+      <c r="O12" s="103"/>
+      <c r="P12" s="103"/>
+      <c r="Q12" s="103"/>
+      <c r="R12" s="103"/>
+      <c r="S12" s="103"/>
+      <c r="T12" s="103"/>
       <c r="U12" s="7"/>
       <c r="V12" s="7"/>
       <c r="W12" s="7"/>
@@ -11384,12 +10449,12 @@
       <c r="Y12" s="7"/>
       <c r="Z12" s="7"/>
       <c r="AA12" s="7"/>
-      <c r="AB12" s="150"/>
-      <c r="AC12" s="150">
+      <c r="AB12" s="122"/>
+      <c r="AC12" s="122">
         <f>IF(AB4=1,AC$2,"")</f>
-        <v>7862714.0960000008</v>
-      </c>
-      <c r="AD12" s="150" t="s">
+        <v>5286472.3040000005</v>
+      </c>
+      <c r="AD12" s="122" t="s">
         <v>30</v>
       </c>
       <c r="AE12" s="7"/>
@@ -11436,12 +10501,12 @@
       <c r="Y13" s="7"/>
       <c r="Z13" s="7"/>
       <c r="AA13" s="7"/>
-      <c r="AB13" s="150"/>
-      <c r="AC13" s="150">
+      <c r="AB13" s="122"/>
+      <c r="AC13" s="122">
         <f>IF(AB4=1,AC$2,"")</f>
-        <v>7862714.0960000008</v>
-      </c>
-      <c r="AD13" s="150" t="s">
+        <v>5286472.3040000005</v>
+      </c>
+      <c r="AD13" s="122" t="s">
         <v>31</v>
       </c>
       <c r="AE13" s="7"/>
@@ -11461,15 +10526,15 @@
       <c r="AS13" s="7"/>
     </row>
     <row r="14" spans="1:45" ht="30" customHeight="1">
-      <c r="A14" s="117"/>
-      <c r="B14" s="117"/>
-      <c r="C14" s="117"/>
-      <c r="D14" s="117"/>
-      <c r="E14" s="117"/>
-      <c r="F14" s="117"/>
-      <c r="G14" s="117"/>
-      <c r="H14" s="117"/>
-      <c r="I14" s="117"/>
+      <c r="A14" s="103"/>
+      <c r="B14" s="103"/>
+      <c r="C14" s="103"/>
+      <c r="D14" s="103"/>
+      <c r="E14" s="103"/>
+      <c r="F14" s="103"/>
+      <c r="G14" s="103"/>
+      <c r="H14" s="103"/>
+      <c r="I14" s="103"/>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
       <c r="L14" s="7"/>
@@ -11488,12 +10553,12 @@
       <c r="Y14" s="7"/>
       <c r="Z14" s="7"/>
       <c r="AA14" s="7"/>
-      <c r="AB14" s="150"/>
-      <c r="AC14" s="150">
+      <c r="AB14" s="122"/>
+      <c r="AC14" s="122">
         <f>IF(AB4=1,AC$2,"")</f>
-        <v>7862714.0960000008</v>
-      </c>
-      <c r="AD14" s="150"/>
+        <v>5286472.3040000005</v>
+      </c>
+      <c r="AD14" s="122"/>
       <c r="AE14" s="7"/>
       <c r="AF14" s="7"/>
       <c r="AG14" s="7"/>
@@ -11511,15 +10576,15 @@
       <c r="AS14" s="7"/>
     </row>
     <row r="15" spans="1:45" ht="31.95" customHeight="1">
-      <c r="A15" s="117"/>
-      <c r="B15" s="117"/>
-      <c r="C15" s="117"/>
-      <c r="D15" s="117"/>
-      <c r="E15" s="117"/>
-      <c r="F15" s="117"/>
-      <c r="G15" s="117"/>
-      <c r="H15" s="117"/>
-      <c r="I15" s="117"/>
+      <c r="A15" s="103"/>
+      <c r="B15" s="103"/>
+      <c r="C15" s="103"/>
+      <c r="D15" s="103"/>
+      <c r="E15" s="103"/>
+      <c r="F15" s="103"/>
+      <c r="G15" s="103"/>
+      <c r="H15" s="103"/>
+      <c r="I15" s="103"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7"/>
       <c r="L15" s="7"/>
@@ -11538,9 +10603,9 @@
       <c r="Y15" s="7"/>
       <c r="Z15" s="7"/>
       <c r="AA15" s="7"/>
-      <c r="AB15" s="150"/>
-      <c r="AC15" s="150"/>
-      <c r="AD15" s="150"/>
+      <c r="AB15" s="122"/>
+      <c r="AC15" s="122"/>
+      <c r="AD15" s="122"/>
       <c r="AE15" s="7"/>
       <c r="AF15" s="7"/>
       <c r="AG15" s="7"/>
@@ -11585,9 +10650,9 @@
       <c r="Y16" s="7"/>
       <c r="Z16" s="7"/>
       <c r="AA16" s="7"/>
-      <c r="AB16" s="150"/>
-      <c r="AC16" s="150"/>
-      <c r="AD16" s="150"/>
+      <c r="AB16" s="122"/>
+      <c r="AC16" s="122"/>
+      <c r="AD16" s="122"/>
       <c r="AE16" s="7"/>
       <c r="AF16" s="7"/>
       <c r="AG16" s="7"/>
@@ -11632,9 +10697,9 @@
       <c r="Y17" s="7"/>
       <c r="Z17" s="7"/>
       <c r="AA17" s="7"/>
-      <c r="AB17" s="150"/>
-      <c r="AC17" s="150"/>
-      <c r="AD17" s="150"/>
+      <c r="AB17" s="122"/>
+      <c r="AC17" s="122"/>
+      <c r="AD17" s="122"/>
       <c r="AE17" s="7"/>
       <c r="AF17" s="7"/>
       <c r="AG17" s="7"/>
@@ -12406,26 +11471,26 @@
     <row r="34" spans="1:45" ht="30" customHeight="1">
       <c r="A34" s="7"/>
       <c r="B34" s="7"/>
-      <c r="C34" s="117"/>
-      <c r="D34" s="117"/>
-      <c r="E34" s="117"/>
-      <c r="F34" s="117"/>
-      <c r="G34" s="117"/>
-      <c r="H34" s="117"/>
-      <c r="I34" s="117"/>
-      <c r="J34" s="117"/>
-      <c r="K34" s="117"/>
-      <c r="L34" s="117"/>
-      <c r="M34" s="117"/>
-      <c r="N34" s="117"/>
-      <c r="O34" s="117"/>
-      <c r="P34" s="117"/>
-      <c r="Q34" s="117"/>
-      <c r="R34" s="117"/>
-      <c r="S34" s="117"/>
-      <c r="T34" s="117"/>
-      <c r="U34" s="117"/>
-      <c r="V34" s="117"/>
+      <c r="C34" s="103"/>
+      <c r="D34" s="103"/>
+      <c r="E34" s="103"/>
+      <c r="F34" s="103"/>
+      <c r="G34" s="103"/>
+      <c r="H34" s="103"/>
+      <c r="I34" s="103"/>
+      <c r="J34" s="103"/>
+      <c r="K34" s="103"/>
+      <c r="L34" s="103"/>
+      <c r="M34" s="103"/>
+      <c r="N34" s="103"/>
+      <c r="O34" s="103"/>
+      <c r="P34" s="103"/>
+      <c r="Q34" s="103"/>
+      <c r="R34" s="103"/>
+      <c r="S34" s="103"/>
+      <c r="T34" s="103"/>
+      <c r="U34" s="103"/>
+      <c r="V34" s="103"/>
       <c r="W34" s="7"/>
       <c r="X34" s="7"/>
       <c r="Y34" s="7"/>
@@ -12453,26 +11518,26 @@
     <row r="35" spans="1:45" ht="30" customHeight="1">
       <c r="A35" s="7"/>
       <c r="B35" s="7"/>
-      <c r="C35" s="117"/>
-      <c r="D35" s="117"/>
-      <c r="E35" s="117"/>
-      <c r="F35" s="117"/>
-      <c r="G35" s="117"/>
-      <c r="H35" s="117"/>
-      <c r="I35" s="117"/>
-      <c r="J35" s="117"/>
-      <c r="K35" s="117"/>
-      <c r="L35" s="117"/>
-      <c r="M35" s="117"/>
-      <c r="N35" s="117"/>
-      <c r="O35" s="117"/>
-      <c r="P35" s="117"/>
-      <c r="Q35" s="117"/>
-      <c r="R35" s="117"/>
-      <c r="S35" s="117"/>
-      <c r="T35" s="117"/>
-      <c r="U35" s="117"/>
-      <c r="V35" s="117"/>
+      <c r="C35" s="103"/>
+      <c r="D35" s="103"/>
+      <c r="E35" s="103"/>
+      <c r="F35" s="103"/>
+      <c r="G35" s="103"/>
+      <c r="H35" s="103"/>
+      <c r="I35" s="103"/>
+      <c r="J35" s="103"/>
+      <c r="K35" s="103"/>
+      <c r="L35" s="103"/>
+      <c r="M35" s="103"/>
+      <c r="N35" s="103"/>
+      <c r="O35" s="103"/>
+      <c r="P35" s="103"/>
+      <c r="Q35" s="103"/>
+      <c r="R35" s="103"/>
+      <c r="S35" s="103"/>
+      <c r="T35" s="103"/>
+      <c r="U35" s="103"/>
+      <c r="V35" s="103"/>
       <c r="W35" s="7"/>
       <c r="X35" s="7"/>
       <c r="Y35" s="7"/>
@@ -12500,26 +11565,26 @@
     <row r="36" spans="1:45" ht="30" customHeight="1">
       <c r="A36" s="7"/>
       <c r="B36" s="7"/>
-      <c r="C36" s="117"/>
-      <c r="D36" s="117"/>
-      <c r="E36" s="117"/>
-      <c r="F36" s="117"/>
-      <c r="G36" s="117"/>
-      <c r="H36" s="117"/>
-      <c r="I36" s="117"/>
-      <c r="J36" s="117"/>
-      <c r="K36" s="117"/>
-      <c r="L36" s="117"/>
-      <c r="M36" s="117"/>
-      <c r="N36" s="117"/>
-      <c r="O36" s="117"/>
-      <c r="P36" s="117"/>
-      <c r="Q36" s="117"/>
-      <c r="R36" s="117"/>
-      <c r="S36" s="117"/>
-      <c r="T36" s="117"/>
-      <c r="U36" s="117"/>
-      <c r="V36" s="117"/>
+      <c r="C36" s="103"/>
+      <c r="D36" s="103"/>
+      <c r="E36" s="103"/>
+      <c r="F36" s="103"/>
+      <c r="G36" s="103"/>
+      <c r="H36" s="103"/>
+      <c r="I36" s="103"/>
+      <c r="J36" s="103"/>
+      <c r="K36" s="103"/>
+      <c r="L36" s="103"/>
+      <c r="M36" s="103"/>
+      <c r="N36" s="103"/>
+      <c r="O36" s="103"/>
+      <c r="P36" s="103"/>
+      <c r="Q36" s="103"/>
+      <c r="R36" s="103"/>
+      <c r="S36" s="103"/>
+      <c r="T36" s="103"/>
+      <c r="U36" s="103"/>
+      <c r="V36" s="103"/>
       <c r="W36" s="7"/>
       <c r="X36" s="7"/>
       <c r="Y36" s="7"/>
@@ -12547,26 +11612,26 @@
     <row r="37" spans="1:45" ht="30" customHeight="1">
       <c r="A37" s="7"/>
       <c r="B37" s="7"/>
-      <c r="C37" s="117"/>
-      <c r="D37" s="117"/>
-      <c r="E37" s="117"/>
-      <c r="F37" s="117"/>
-      <c r="G37" s="117"/>
-      <c r="H37" s="117"/>
-      <c r="I37" s="117"/>
-      <c r="J37" s="117"/>
-      <c r="K37" s="117"/>
-      <c r="L37" s="117"/>
-      <c r="M37" s="117"/>
-      <c r="N37" s="117"/>
-      <c r="O37" s="117"/>
-      <c r="P37" s="117"/>
-      <c r="Q37" s="117"/>
-      <c r="R37" s="117"/>
-      <c r="S37" s="117"/>
-      <c r="T37" s="117"/>
-      <c r="U37" s="117"/>
-      <c r="V37" s="117"/>
+      <c r="C37" s="103"/>
+      <c r="D37" s="103"/>
+      <c r="E37" s="103"/>
+      <c r="F37" s="103"/>
+      <c r="G37" s="103"/>
+      <c r="H37" s="103"/>
+      <c r="I37" s="103"/>
+      <c r="J37" s="103"/>
+      <c r="K37" s="103"/>
+      <c r="L37" s="103"/>
+      <c r="M37" s="103"/>
+      <c r="N37" s="103"/>
+      <c r="O37" s="103"/>
+      <c r="P37" s="103"/>
+      <c r="Q37" s="103"/>
+      <c r="R37" s="103"/>
+      <c r="S37" s="103"/>
+      <c r="T37" s="103"/>
+      <c r="U37" s="103"/>
+      <c r="V37" s="103"/>
       <c r="W37" s="7"/>
       <c r="X37" s="7"/>
       <c r="Y37" s="7"/>
@@ -12593,9 +11658,9 @@
     </row>
     <row r="38" spans="1:45" ht="30" customHeight="1">
       <c r="A38" s="7"/>
-      <c r="B38" s="117"/>
-      <c r="C38" s="117"/>
-      <c r="D38" s="117"/>
+      <c r="B38" s="103"/>
+      <c r="C38" s="103"/>
+      <c r="D38" s="103"/>
       <c r="E38" s="7"/>
       <c r="F38" s="7"/>
       <c r="G38" s="7"/>
@@ -12608,12 +11673,12 @@
       <c r="N38" s="7"/>
       <c r="O38" s="7"/>
       <c r="P38" s="7"/>
-      <c r="Q38" s="117"/>
-      <c r="R38" s="117"/>
-      <c r="S38" s="117"/>
-      <c r="T38" s="117"/>
-      <c r="U38" s="117"/>
-      <c r="V38" s="117"/>
+      <c r="Q38" s="103"/>
+      <c r="R38" s="103"/>
+      <c r="S38" s="103"/>
+      <c r="T38" s="103"/>
+      <c r="U38" s="103"/>
+      <c r="V38" s="103"/>
       <c r="W38" s="7"/>
       <c r="X38" s="7"/>
       <c r="Y38" s="7"/>
@@ -12640,27 +11705,27 @@
     </row>
     <row r="39" spans="1:45" ht="30" customHeight="1">
       <c r="A39" s="7"/>
-      <c r="B39" s="117"/>
-      <c r="C39" s="117"/>
-      <c r="D39" s="117"/>
-      <c r="E39" s="117"/>
-      <c r="F39" s="117"/>
-      <c r="G39" s="117"/>
-      <c r="H39" s="117"/>
-      <c r="I39" s="117"/>
-      <c r="J39" s="117"/>
-      <c r="K39" s="117"/>
-      <c r="L39" s="117"/>
-      <c r="M39" s="117"/>
-      <c r="N39" s="117"/>
-      <c r="O39" s="117"/>
-      <c r="P39" s="117"/>
-      <c r="Q39" s="117"/>
-      <c r="R39" s="117"/>
-      <c r="S39" s="117"/>
-      <c r="T39" s="117"/>
-      <c r="U39" s="117"/>
-      <c r="V39" s="117"/>
+      <c r="B39" s="103"/>
+      <c r="C39" s="103"/>
+      <c r="D39" s="103"/>
+      <c r="E39" s="103"/>
+      <c r="F39" s="103"/>
+      <c r="G39" s="103"/>
+      <c r="H39" s="103"/>
+      <c r="I39" s="103"/>
+      <c r="J39" s="103"/>
+      <c r="K39" s="103"/>
+      <c r="L39" s="103"/>
+      <c r="M39" s="103"/>
+      <c r="N39" s="103"/>
+      <c r="O39" s="103"/>
+      <c r="P39" s="103"/>
+      <c r="Q39" s="103"/>
+      <c r="R39" s="103"/>
+      <c r="S39" s="103"/>
+      <c r="T39" s="103"/>
+      <c r="U39" s="103"/>
+      <c r="V39" s="103"/>
       <c r="W39" s="7"/>
       <c r="X39" s="7"/>
       <c r="Y39" s="7"/>
@@ -12738,18 +11803,18 @@
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
       <c r="E41" s="7"/>
-      <c r="F41" s="117"/>
-      <c r="G41" s="117"/>
-      <c r="H41" s="117"/>
-      <c r="I41" s="117"/>
-      <c r="J41" s="117"/>
-      <c r="K41" s="117"/>
-      <c r="L41" s="117"/>
-      <c r="M41" s="117"/>
-      <c r="N41" s="117"/>
-      <c r="O41" s="117"/>
-      <c r="P41" s="117"/>
-      <c r="Q41" s="117"/>
+      <c r="F41" s="103"/>
+      <c r="G41" s="103"/>
+      <c r="H41" s="103"/>
+      <c r="I41" s="103"/>
+      <c r="J41" s="103"/>
+      <c r="K41" s="103"/>
+      <c r="L41" s="103"/>
+      <c r="M41" s="103"/>
+      <c r="N41" s="103"/>
+      <c r="O41" s="103"/>
+      <c r="P41" s="103"/>
+      <c r="Q41" s="103"/>
       <c r="R41" s="7"/>
       <c r="S41" s="7"/>
       <c r="T41" s="7"/>
@@ -12785,18 +11850,18 @@
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
       <c r="E42" s="7"/>
-      <c r="F42" s="117"/>
-      <c r="G42" s="117"/>
-      <c r="H42" s="117"/>
-      <c r="I42" s="117"/>
-      <c r="J42" s="117"/>
-      <c r="K42" s="117"/>
-      <c r="L42" s="117"/>
-      <c r="M42" s="117"/>
-      <c r="N42" s="117"/>
-      <c r="O42" s="117"/>
-      <c r="P42" s="117"/>
-      <c r="Q42" s="117"/>
+      <c r="F42" s="103"/>
+      <c r="G42" s="103"/>
+      <c r="H42" s="103"/>
+      <c r="I42" s="103"/>
+      <c r="J42" s="103"/>
+      <c r="K42" s="103"/>
+      <c r="L42" s="103"/>
+      <c r="M42" s="103"/>
+      <c r="N42" s="103"/>
+      <c r="O42" s="103"/>
+      <c r="P42" s="103"/>
+      <c r="Q42" s="103"/>
       <c r="R42" s="7"/>
       <c r="S42" s="7"/>
       <c r="T42" s="7"/>
@@ -12927,27 +11992,27 @@
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
       <c r="F45" s="7"/>
-      <c r="G45" s="125"/>
-      <c r="H45" s="126"/>
-      <c r="I45" s="126"/>
-      <c r="J45" s="126"/>
-      <c r="K45" s="126"/>
-      <c r="L45" s="126"/>
-      <c r="M45" s="126"/>
-      <c r="N45" s="126"/>
-      <c r="O45" s="126"/>
-      <c r="P45" s="126"/>
-      <c r="Q45" s="126"/>
-      <c r="R45" s="126"/>
-      <c r="S45" s="126"/>
-      <c r="T45" s="126"/>
-      <c r="U45" s="126"/>
-      <c r="V45" s="126"/>
-      <c r="W45" s="126"/>
-      <c r="X45" s="126"/>
-      <c r="Y45" s="126"/>
-      <c r="Z45" s="126"/>
-      <c r="AA45" s="126"/>
+      <c r="G45" s="201"/>
+      <c r="H45" s="202"/>
+      <c r="I45" s="202"/>
+      <c r="J45" s="202"/>
+      <c r="K45" s="202"/>
+      <c r="L45" s="202"/>
+      <c r="M45" s="202"/>
+      <c r="N45" s="202"/>
+      <c r="O45" s="202"/>
+      <c r="P45" s="202"/>
+      <c r="Q45" s="202"/>
+      <c r="R45" s="202"/>
+      <c r="S45" s="202"/>
+      <c r="T45" s="202"/>
+      <c r="U45" s="202"/>
+      <c r="V45" s="202"/>
+      <c r="W45" s="202"/>
+      <c r="X45" s="202"/>
+      <c r="Y45" s="202"/>
+      <c r="Z45" s="202"/>
+      <c r="AA45" s="202"/>
       <c r="AB45" s="7"/>
       <c r="AC45" s="7"/>
       <c r="AD45" s="7"/>
@@ -13027,12 +12092,12 @@
       <c r="J47" s="7"/>
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
-      <c r="M47" s="139"/>
-      <c r="N47" s="140"/>
-      <c r="O47" s="140"/>
-      <c r="P47" s="140"/>
-      <c r="Q47" s="140"/>
-      <c r="R47" s="141"/>
+      <c r="M47" s="113"/>
+      <c r="N47" s="114"/>
+      <c r="O47" s="114"/>
+      <c r="P47" s="114"/>
+      <c r="Q47" s="114"/>
+      <c r="R47" s="115"/>
       <c r="S47" s="7"/>
       <c r="T47" s="7"/>
       <c r="U47" s="7"/>
@@ -13074,12 +12139,12 @@
       <c r="J48" s="7"/>
       <c r="K48" s="7"/>
       <c r="L48" s="7"/>
-      <c r="M48" s="142"/>
-      <c r="N48" s="143"/>
-      <c r="O48" s="143"/>
-      <c r="P48" s="143"/>
-      <c r="Q48" s="143"/>
-      <c r="R48" s="144"/>
+      <c r="M48" s="116"/>
+      <c r="N48" s="117"/>
+      <c r="O48" s="117"/>
+      <c r="P48" s="117"/>
+      <c r="Q48" s="117"/>
+      <c r="R48" s="118"/>
       <c r="S48" s="7"/>
       <c r="T48" s="7"/>
       <c r="U48" s="7"/>
@@ -13121,12 +12186,12 @@
       <c r="J49" s="7"/>
       <c r="K49" s="7"/>
       <c r="L49" s="7"/>
-      <c r="M49" s="142"/>
-      <c r="N49" s="143"/>
-      <c r="O49" s="143"/>
-      <c r="P49" s="143"/>
-      <c r="Q49" s="143"/>
-      <c r="R49" s="144"/>
+      <c r="M49" s="116"/>
+      <c r="N49" s="117"/>
+      <c r="O49" s="117"/>
+      <c r="P49" s="117"/>
+      <c r="Q49" s="117"/>
+      <c r="R49" s="118"/>
       <c r="S49" s="7"/>
       <c r="T49" s="7"/>
       <c r="U49" s="7"/>
@@ -13168,12 +12233,12 @@
       <c r="J50" s="7"/>
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
-      <c r="M50" s="142"/>
-      <c r="N50" s="143"/>
-      <c r="O50" s="143"/>
-      <c r="P50" s="143"/>
-      <c r="Q50" s="143"/>
-      <c r="R50" s="144"/>
+      <c r="M50" s="116"/>
+      <c r="N50" s="117"/>
+      <c r="O50" s="117"/>
+      <c r="P50" s="117"/>
+      <c r="Q50" s="117"/>
+      <c r="R50" s="118"/>
       <c r="S50" s="7"/>
       <c r="T50" s="7"/>
       <c r="U50" s="7"/>
@@ -13215,12 +12280,12 @@
       <c r="J51" s="7"/>
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
-      <c r="M51" s="142"/>
-      <c r="N51" s="143"/>
-      <c r="O51" s="143"/>
-      <c r="P51" s="143"/>
-      <c r="Q51" s="143"/>
-      <c r="R51" s="144"/>
+      <c r="M51" s="116"/>
+      <c r="N51" s="117"/>
+      <c r="O51" s="117"/>
+      <c r="P51" s="117"/>
+      <c r="Q51" s="117"/>
+      <c r="R51" s="118"/>
       <c r="S51" s="7"/>
       <c r="T51" s="7"/>
       <c r="U51" s="7"/>
@@ -13262,12 +12327,12 @@
       <c r="J52" s="7"/>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
-      <c r="M52" s="145"/>
-      <c r="N52" s="146"/>
-      <c r="O52" s="146"/>
-      <c r="P52" s="146"/>
-      <c r="Q52" s="146"/>
-      <c r="R52" s="147"/>
+      <c r="M52" s="119"/>
+      <c r="N52" s="120"/>
+      <c r="O52" s="120"/>
+      <c r="P52" s="120"/>
+      <c r="Q52" s="120"/>
+      <c r="R52" s="121"/>
       <c r="S52" s="7"/>
       <c r="T52" s="7"/>
       <c r="U52" s="7"/>
@@ -13767,27 +12832,27 @@
       <c r="AS62" s="7"/>
     </row>
     <row r="63" spans="1:45" ht="18" customHeight="1">
-      <c r="A63" s="117"/>
-      <c r="B63" s="117"/>
-      <c r="C63" s="117"/>
-      <c r="D63" s="117"/>
-      <c r="E63" s="117"/>
-      <c r="F63" s="117"/>
-      <c r="G63" s="117"/>
-      <c r="H63" s="117"/>
-      <c r="I63" s="117"/>
-      <c r="J63" s="117"/>
-      <c r="K63" s="117"/>
-      <c r="L63" s="117"/>
-      <c r="M63" s="117"/>
-      <c r="N63" s="117"/>
-      <c r="O63" s="117"/>
-      <c r="P63" s="117"/>
-      <c r="Q63" s="117"/>
-      <c r="R63" s="117"/>
-      <c r="S63" s="117"/>
-      <c r="T63" s="117"/>
-      <c r="U63" s="117"/>
+      <c r="A63" s="103"/>
+      <c r="B63" s="103"/>
+      <c r="C63" s="103"/>
+      <c r="D63" s="103"/>
+      <c r="E63" s="103"/>
+      <c r="F63" s="103"/>
+      <c r="G63" s="103"/>
+      <c r="H63" s="103"/>
+      <c r="I63" s="103"/>
+      <c r="J63" s="103"/>
+      <c r="K63" s="103"/>
+      <c r="L63" s="103"/>
+      <c r="M63" s="103"/>
+      <c r="N63" s="103"/>
+      <c r="O63" s="103"/>
+      <c r="P63" s="103"/>
+      <c r="Q63" s="103"/>
+      <c r="R63" s="103"/>
+      <c r="S63" s="103"/>
+      <c r="T63" s="103"/>
+      <c r="U63" s="103"/>
       <c r="V63" s="7"/>
       <c r="W63" s="7"/>
       <c r="X63" s="7"/>
@@ -13955,27 +13020,27 @@
       <c r="AS66" s="7"/>
     </row>
     <row r="67" spans="1:45">
-      <c r="A67" s="148"/>
-      <c r="B67" s="149"/>
-      <c r="C67" s="149"/>
-      <c r="D67" s="149"/>
-      <c r="E67" s="149"/>
-      <c r="F67" s="149"/>
-      <c r="G67" s="149"/>
-      <c r="H67" s="149"/>
-      <c r="I67" s="149"/>
-      <c r="J67" s="149"/>
-      <c r="K67" s="149"/>
-      <c r="L67" s="149"/>
-      <c r="M67" s="149"/>
-      <c r="N67" s="149"/>
-      <c r="O67" s="149"/>
-      <c r="P67" s="149"/>
-      <c r="Q67" s="149"/>
-      <c r="R67" s="149"/>
-      <c r="S67" s="149"/>
-      <c r="T67" s="149"/>
-      <c r="U67" s="149"/>
+      <c r="A67" s="193"/>
+      <c r="B67" s="194"/>
+      <c r="C67" s="194"/>
+      <c r="D67" s="194"/>
+      <c r="E67" s="194"/>
+      <c r="F67" s="194"/>
+      <c r="G67" s="194"/>
+      <c r="H67" s="194"/>
+      <c r="I67" s="194"/>
+      <c r="J67" s="194"/>
+      <c r="K67" s="194"/>
+      <c r="L67" s="194"/>
+      <c r="M67" s="194"/>
+      <c r="N67" s="194"/>
+      <c r="O67" s="194"/>
+      <c r="P67" s="194"/>
+      <c r="Q67" s="194"/>
+      <c r="R67" s="194"/>
+      <c r="S67" s="194"/>
+      <c r="T67" s="194"/>
+      <c r="U67" s="194"/>
       <c r="V67" s="7"/>
       <c r="W67" s="7"/>
       <c r="X67" s="7"/>
@@ -18844,11 +17909,22 @@
     </row>
   </sheetData>
   <mergeCells count="55">
-    <mergeCell ref="A1:U1"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="A4:U4"/>
-    <mergeCell ref="M5:P9"/>
-    <mergeCell ref="P10:Q11"/>
+    <mergeCell ref="G45:AA45"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="G7:H7"/>
     <mergeCell ref="A67:U67"/>
     <mergeCell ref="I3:J3"/>
     <mergeCell ref="I5:J5"/>
@@ -18862,10 +17938,23 @@
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="A4:U4"/>
+    <mergeCell ref="M5:P9"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="Q5:T9"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="P10:Q11"/>
     <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="I8:J8"/>
     <mergeCell ref="D10:F10"/>
     <mergeCell ref="K8:L8"/>
     <mergeCell ref="K5:L5"/>
@@ -18873,32 +17962,8 @@
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="G11:I11"/>
-    <mergeCell ref="G45:AA45"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="Q5:T9"/>
     <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I8:J8"/>
   </mergeCells>
   <conditionalFormatting sqref="N48:R52">
     <cfRule type="colorScale" priority="1">
@@ -50755,7 +49820,7 @@
       <c r="U1" s="14"/>
     </row>
     <row r="2" spans="1:21" ht="12.6" customHeight="1">
-      <c r="A2" s="171" t="s">
+      <c r="A2" s="139" t="s">
         <v>95</v>
       </c>
       <c r="B2" s="13"/>
@@ -50816,7 +49881,7 @@
       <c r="I4" s="16"/>
       <c r="J4" s="16"/>
       <c r="K4" s="16"/>
-      <c r="L4" s="187" t="s">
+      <c r="L4" s="146" t="s">
         <v>170</v>
       </c>
       <c r="N4" s="14"/>
@@ -50862,7 +49927,7 @@
       <c r="K5" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="L5" s="189" t="s">
+      <c r="L5" s="207" t="s">
         <v>168</v>
       </c>
       <c r="N5" s="14"/>
@@ -50875,12 +49940,12 @@
       <c r="U5" s="14"/>
     </row>
     <row r="6" spans="1:21" ht="21" customHeight="1">
-      <c r="A6" s="170" t="s">
+      <c r="A6" s="138" t="s">
         <v>98</v>
       </c>
       <c r="B6" s="20">
         <f>Dashboard!A3</f>
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C6" s="20" t="str">
         <f>Dashboard!C3</f>
@@ -50918,7 +49983,7 @@
         <f>Dashboard!S3</f>
         <v>ON</v>
       </c>
-      <c r="L6" s="189"/>
+      <c r="L6" s="207"/>
       <c r="N6" s="14"/>
       <c r="O6" s="14"/>
       <c r="P6" s="14"/>
@@ -50934,7 +49999,7 @@
       </c>
       <c r="B7" s="23">
         <f t="shared" ref="B7:K7" si="0">B6</f>
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C7" s="23" t="str">
         <f t="shared" si="0"/>
@@ -50972,7 +50037,7 @@
         <f t="shared" si="0"/>
         <v>ON</v>
       </c>
-      <c r="L7" s="188" t="s">
+      <c r="L7" s="147" t="s">
         <v>169</v>
       </c>
       <c r="N7" s="14"/>
@@ -51949,7 +51014,7 @@
       </c>
       <c r="B42" s="33">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$42)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])</f>
-        <v>798620.35000000009</v>
+        <v>504544.72999999992</v>
       </c>
       <c r="C42" s="33">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$42)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*((SalesData[Units]&lt;&gt;0)))</f>
@@ -51957,31 +51022,31 @@
       </c>
       <c r="D42" s="33">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$42)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Units])</f>
-        <v>463</v>
+        <v>264</v>
       </c>
       <c r="E42" s="33">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$42)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Cost])</f>
-        <v>495144.60999999993</v>
+        <v>312817.73</v>
       </c>
       <c r="F42" s="33">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$42)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Profit])</f>
-        <v>303475.74</v>
+        <v>191727</v>
       </c>
       <c r="G42" s="34">
         <f t="shared" ref="G42:G53" si="1">IFERROR(B42/SUM($B$42:$B$53),0)</f>
-        <v>0.16251291149579655</v>
+        <v>0.15270515413259222</v>
       </c>
       <c r="H42" s="34">
         <f>IF(NOT(ISNUMBER($B$6)),"n/a",IF($B$6&lt;=2022,"n/a",IFERROR((B42-SUMPRODUCT((SalesData[MonthNum]=$A$42)*(SalesData[Year]=$B$6-1)*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue]))/SUMPRODUCT((SalesData[MonthNum]=$A$42)*(SalesData[Year]=$B$6-1)*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue]),"n/a")))</f>
-        <v>0.58285341717869144</v>
+        <v>0.75006964971879986</v>
       </c>
       <c r="I42" s="35">
         <f>B42*Dashboard!$AB$2</f>
-        <v>798620.35000000009</v>
+        <v>504544.72999999992</v>
       </c>
       <c r="J42" s="36">
         <f>F42*Dashboard!$AB$2</f>
-        <v>303475.74</v>
+        <v>191727</v>
       </c>
       <c r="K42" s="14"/>
       <c r="L42" s="14"/>
@@ -52001,7 +51066,7 @@
       </c>
       <c r="B43" s="38">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$43)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])</f>
-        <v>384847.49</v>
+        <v>60199.479999999996</v>
       </c>
       <c r="C43" s="38">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$43)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*((SalesData[Units]&lt;&gt;0)))</f>
@@ -52009,31 +51074,31 @@
       </c>
       <c r="D43" s="38">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$43)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Units])</f>
-        <v>197</v>
+        <v>154</v>
       </c>
       <c r="E43" s="38">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$43)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Cost])</f>
-        <v>238605.45</v>
+        <v>37323.69000000001</v>
       </c>
       <c r="F43" s="38">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$43)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Profit])</f>
-        <v>146242.03999999998</v>
+        <v>22875.79</v>
       </c>
       <c r="G43" s="39">
         <f t="shared" si="1"/>
-        <v>7.8313413979182275E-2</v>
+        <v>1.821993239747426E-2</v>
       </c>
       <c r="H43" s="39">
         <f>IF(NOT(ISNUMBER($B$6)),"n/a",IF($B$6&lt;=2022,"n/a",IFERROR((B43-SUMPRODUCT((SalesData[MonthNum]=$A$43)*(SalesData[Year]=$B$6-1)*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue]))/SUMPRODUCT((SalesData[MonthNum]=$A$43)*(SalesData[Year]=$B$6-1)*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue]),"n/a")))</f>
-        <v>5.3928706693147523</v>
+        <v>-0.76386853828224188</v>
       </c>
       <c r="I43" s="40">
         <f>B43*Dashboard!$AB$2</f>
-        <v>384847.49</v>
+        <v>60199.479999999996</v>
       </c>
       <c r="J43" s="41">
         <f>F43*Dashboard!$AB$2</f>
-        <v>146242.03999999998</v>
+        <v>22875.79</v>
       </c>
       <c r="K43" s="14"/>
       <c r="L43" s="14"/>
@@ -52053,7 +51118,7 @@
       </c>
       <c r="B44" s="11">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$44)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])</f>
-        <v>75262.539999999994</v>
+        <v>53806.63</v>
       </c>
       <c r="C44" s="11">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$44)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*((SalesData[Units]&lt;&gt;0)))</f>
@@ -52061,31 +51126,31 @@
       </c>
       <c r="D44" s="11">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$44)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Units])</f>
-        <v>206</v>
+        <v>166</v>
       </c>
       <c r="E44" s="11">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$44)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Cost])</f>
-        <v>46662.78</v>
+        <v>33360.109999999993</v>
       </c>
       <c r="F44" s="11">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$44)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Profit])</f>
-        <v>28599.760000000002</v>
+        <v>20446.52</v>
       </c>
       <c r="G44" s="43">
         <f t="shared" si="1"/>
-        <v>1.5315330371895539E-2</v>
+        <v>1.6285076899931868E-2</v>
       </c>
       <c r="H44" s="43">
         <f>IF(NOT(ISNUMBER($B$6)),"n/a",IF($B$6&lt;=2022,"n/a",IFERROR((B44-SUMPRODUCT((SalesData[MonthNum]=$A$44)*(SalesData[Year]=$B$6-1)*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue]))/SUMPRODUCT((SalesData[MonthNum]=$A$44)*(SalesData[Year]=$B$6-1)*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue]),"n/a")))</f>
-        <v>0.39875959523947135</v>
+        <v>-0.74712437593121839</v>
       </c>
       <c r="I44" s="44">
         <f>B44*Dashboard!$AB$2</f>
-        <v>75262.539999999994</v>
+        <v>53806.63</v>
       </c>
       <c r="J44" s="45">
         <f>F44*Dashboard!$AB$2</f>
-        <v>28599.760000000002</v>
+        <v>20446.52</v>
       </c>
       <c r="K44" s="14"/>
       <c r="L44" s="14"/>
@@ -52105,7 +51170,7 @@
       </c>
       <c r="B45" s="38">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$45)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])</f>
-        <v>431756.67000000004</v>
+        <v>490493.69000000006</v>
       </c>
       <c r="C45" s="38">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$45)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*((SalesData[Units]&lt;&gt;0)))</f>
@@ -52113,31 +51178,31 @@
       </c>
       <c r="D45" s="38">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$45)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Units])</f>
-        <v>262</v>
+        <v>239</v>
       </c>
       <c r="E45" s="38">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$45)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Cost])</f>
-        <v>267689.12000000005</v>
+        <v>304106.09999999998</v>
       </c>
       <c r="F45" s="38">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$45)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Profit])</f>
-        <v>164067.55000000002</v>
+        <v>186387.59</v>
       </c>
       <c r="G45" s="39">
         <f t="shared" si="1"/>
-        <v>8.7859060314991771E-2</v>
+        <v>0.14845247622052049</v>
       </c>
       <c r="H45" s="39">
         <f>IF(NOT(ISNUMBER($B$6)),"n/a",IF($B$6&lt;=2022,"n/a",IFERROR((B45-SUMPRODUCT((SalesData[MonthNum]=$A$45)*(SalesData[Year]=$B$6-1)*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue]))/SUMPRODUCT((SalesData[MonthNum]=$A$45)*(SalesData[Year]=$B$6-1)*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue]),"n/a")))</f>
-        <v>-0.11975081677401397</v>
+        <v>2.0178605499147948</v>
       </c>
       <c r="I45" s="40">
         <f>B45*Dashboard!$AB$2</f>
-        <v>431756.67000000004</v>
+        <v>490493.69000000006</v>
       </c>
       <c r="J45" s="41">
         <f>F45*Dashboard!$AB$2</f>
-        <v>164067.55000000002</v>
+        <v>186387.59</v>
       </c>
       <c r="K45" s="14"/>
       <c r="L45" s="14"/>
@@ -52157,7 +51222,7 @@
       </c>
       <c r="B46" s="11">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$46)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])</f>
-        <v>208424.18</v>
+        <v>220014.36000000004</v>
       </c>
       <c r="C46" s="11">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$46)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*((SalesData[Units]&lt;&gt;0)))</f>
@@ -52165,31 +51230,31 @@
       </c>
       <c r="D46" s="11">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$46)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Units])</f>
-        <v>268</v>
+        <v>204</v>
       </c>
       <c r="E46" s="11">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$46)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Cost])</f>
-        <v>129222.99</v>
+        <v>136408.91999999998</v>
       </c>
       <c r="F46" s="11">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$46)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Profit])</f>
-        <v>79201.190000000017</v>
+        <v>83605.440000000002</v>
       </c>
       <c r="G46" s="43">
         <f t="shared" si="1"/>
-        <v>4.2412668695361901E-2</v>
+        <v>6.6589391896301531E-2</v>
       </c>
       <c r="H46" s="43">
         <f>IF(NOT(ISNUMBER($B$6)),"n/a",IF($B$6&lt;=2022,"n/a",IFERROR((B46-SUMPRODUCT((SalesData[MonthNum]=$A$46)*(SalesData[Year]=$B$6-1)*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue]))/SUMPRODUCT((SalesData[MonthNum]=$A$46)*(SalesData[Year]=$B$6-1)*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue]),"n/a")))</f>
-        <v>-5.2679197848722457E-2</v>
+        <v>3.0682210941247265</v>
       </c>
       <c r="I46" s="44">
         <f>B46*Dashboard!$AB$2</f>
-        <v>208424.18</v>
+        <v>220014.36000000004</v>
       </c>
       <c r="J46" s="45">
         <f>F46*Dashboard!$AB$2</f>
-        <v>79201.190000000017</v>
+        <v>83605.440000000002</v>
       </c>
       <c r="K46" s="14"/>
       <c r="L46" s="14"/>
@@ -52209,7 +51274,7 @@
       </c>
       <c r="B47" s="38">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$47)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])</f>
-        <v>270459.49</v>
+        <v>321726.38</v>
       </c>
       <c r="C47" s="38">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$47)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*((SalesData[Units]&lt;&gt;0)))</f>
@@ -52217,31 +51282,31 @@
       </c>
       <c r="D47" s="38">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$47)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Units])</f>
-        <v>280</v>
+        <v>169</v>
       </c>
       <c r="E47" s="38">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$47)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Cost])</f>
-        <v>167684.87</v>
+        <v>199470.37000000002</v>
       </c>
       <c r="F47" s="38">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$47)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Profit])</f>
-        <v>102774.62</v>
+        <v>122256.01000000001</v>
       </c>
       <c r="G47" s="39">
         <f t="shared" si="1"/>
-        <v>5.5036362599035028E-2</v>
+        <v>9.7373480536445081E-2</v>
       </c>
       <c r="H47" s="39">
         <f>IF(NOT(ISNUMBER($B$6)),"n/a",IF($B$6&lt;=2022,"n/a",IFERROR((B47-SUMPRODUCT((SalesData[MonthNum]=$A$47)*(SalesData[Year]=$B$6-1)*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue]))/SUMPRODUCT((SalesData[MonthNum]=$A$47)*(SalesData[Year]=$B$6-1)*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue]),"n/a")))</f>
-        <v>-0.15934935145821744</v>
+        <v>0.47819100429352418</v>
       </c>
       <c r="I47" s="40">
         <f>B47*Dashboard!$AB$2</f>
-        <v>270459.49</v>
+        <v>321726.38</v>
       </c>
       <c r="J47" s="41">
         <f>F47*Dashboard!$AB$2</f>
-        <v>102774.62</v>
+        <v>122256.01000000001</v>
       </c>
       <c r="K47" s="14"/>
       <c r="L47" s="14"/>
@@ -52261,7 +51326,7 @@
       </c>
       <c r="B48" s="11">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$48)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])</f>
-        <v>490806.39999999997</v>
+        <v>218639.71</v>
       </c>
       <c r="C48" s="11">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$48)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*((SalesData[Units]&lt;&gt;0)))</f>
@@ -52269,31 +51334,31 @@
       </c>
       <c r="D48" s="11">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$48)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Units])</f>
-        <v>325</v>
+        <v>234</v>
       </c>
       <c r="E48" s="11">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$48)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Cost])</f>
-        <v>304299.95999999996</v>
+        <v>135556.62000000002</v>
       </c>
       <c r="F48" s="11">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$48)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Profit])</f>
-        <v>186506.44</v>
+        <v>83083.09</v>
       </c>
       <c r="G48" s="43">
         <f t="shared" si="1"/>
-        <v>9.9875212351864695E-2</v>
+        <v>6.6173341291376225E-2</v>
       </c>
       <c r="H48" s="43">
         <f>IF(NOT(ISNUMBER($B$6)),"n/a",IF($B$6&lt;=2022,"n/a",IFERROR((B48-SUMPRODUCT((SalesData[MonthNum]=$A$48)*(SalesData[Year]=$B$6-1)*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue]))/SUMPRODUCT((SalesData[MonthNum]=$A$48)*(SalesData[Year]=$B$6-1)*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue]),"n/a")))</f>
-        <v>1.2448181988532638</v>
+        <v>0.10307548791882505</v>
       </c>
       <c r="I48" s="44">
         <f>B48*Dashboard!$AB$2</f>
-        <v>490806.39999999997</v>
+        <v>218639.71</v>
       </c>
       <c r="J48" s="45">
         <f>F48*Dashboard!$AB$2</f>
-        <v>186506.44</v>
+        <v>83083.09</v>
       </c>
       <c r="K48" s="14"/>
       <c r="L48" s="14"/>
@@ -52313,7 +51378,7 @@
       </c>
       <c r="B49" s="38">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$49)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])</f>
-        <v>383846.58999999997</v>
+        <v>321530.51</v>
       </c>
       <c r="C49" s="38">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$49)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*((SalesData[Units]&lt;&gt;0)))</f>
@@ -52321,31 +51386,31 @@
       </c>
       <c r="D49" s="38">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$49)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Units])</f>
-        <v>293</v>
+        <v>209</v>
       </c>
       <c r="E49" s="38">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$49)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Cost])</f>
-        <v>237984.9</v>
+        <v>199348.9</v>
       </c>
       <c r="F49" s="38">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$49)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Profit])</f>
-        <v>145861.68999999997</v>
+        <v>122181.61</v>
       </c>
       <c r="G49" s="39">
         <f t="shared" si="1"/>
-        <v>7.8109738762145609E-2</v>
+        <v>9.7314198659613368E-2</v>
       </c>
       <c r="H49" s="39">
         <f>IF(NOT(ISNUMBER($B$6)),"n/a",IF($B$6&lt;=2022,"n/a",IFERROR((B49-SUMPRODUCT((SalesData[MonthNum]=$A$49)*(SalesData[Year]=$B$6-1)*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue]))/SUMPRODUCT((SalesData[MonthNum]=$A$49)*(SalesData[Year]=$B$6-1)*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue]),"n/a")))</f>
-        <v>0.19381078330638032</v>
+        <v>1.5624616264946938</v>
       </c>
       <c r="I49" s="40">
         <f>B49*Dashboard!$AB$2</f>
-        <v>383846.58999999997</v>
+        <v>321530.51</v>
       </c>
       <c r="J49" s="41">
         <f>F49*Dashboard!$AB$2</f>
-        <v>145861.68999999997</v>
+        <v>122181.61</v>
       </c>
       <c r="K49" s="14"/>
       <c r="L49" s="14"/>
@@ -52365,7 +51430,7 @@
       </c>
       <c r="B50" s="11">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$50)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])</f>
-        <v>472693.69</v>
+        <v>267610.3899999999</v>
       </c>
       <c r="C50" s="11">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$50)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*((SalesData[Units]&lt;&gt;0)))</f>
@@ -52373,31 +51438,31 @@
       </c>
       <c r="D50" s="11">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$50)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Units])</f>
-        <v>390</v>
+        <v>176</v>
       </c>
       <c r="E50" s="11">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$50)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Cost])</f>
-        <v>293070.07999999996</v>
+        <v>165918.45999999996</v>
       </c>
       <c r="F50" s="11">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$50)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Profit])</f>
-        <v>179623.61000000002</v>
+        <v>101691.93000000001</v>
       </c>
       <c r="G50" s="43">
         <f t="shared" si="1"/>
-        <v>9.6189419425126696E-2</v>
+        <v>8.0994772955874705E-2</v>
       </c>
       <c r="H50" s="43">
         <f>IF(NOT(ISNUMBER($B$6)),"n/a",IF($B$6&lt;=2022,"n/a",IFERROR((B50-SUMPRODUCT((SalesData[MonthNum]=$A$50)*(SalesData[Year]=$B$6-1)*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue]))/SUMPRODUCT((SalesData[MonthNum]=$A$50)*(SalesData[Year]=$B$6-1)*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue]),"n/a")))</f>
-        <v>0.76635029006160849</v>
+        <v>1.427102763534851E-2</v>
       </c>
       <c r="I50" s="44">
         <f>B50*Dashboard!$AB$2</f>
-        <v>472693.69</v>
+        <v>267610.3899999999</v>
       </c>
       <c r="J50" s="45">
         <f>F50*Dashboard!$AB$2</f>
-        <v>179623.61000000002</v>
+        <v>101691.93000000001</v>
       </c>
       <c r="K50" s="14"/>
       <c r="L50" s="14"/>
@@ -52417,7 +51482,7 @@
       </c>
       <c r="B51" s="38">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$51)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])</f>
-        <v>156417.44000000003</v>
+        <v>98548.020000000019</v>
       </c>
       <c r="C51" s="38">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$51)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*((SalesData[Units]&lt;&gt;0)))</f>
@@ -52425,31 +51490,31 @@
       </c>
       <c r="D51" s="38">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$51)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Units])</f>
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="E51" s="38">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$51)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Cost])</f>
-        <v>96978.81</v>
+        <v>61099.78</v>
       </c>
       <c r="F51" s="38">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$51)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Profit])</f>
-        <v>59438.630000000005</v>
+        <v>37448.239999999998</v>
       </c>
       <c r="G51" s="39">
         <f t="shared" si="1"/>
-        <v>3.1829709301946875E-2</v>
+        <v>2.9826474619131956E-2</v>
       </c>
       <c r="H51" s="39">
         <f>IF(NOT(ISNUMBER($B$6)),"n/a",IF($B$6&lt;=2022,"n/a",IFERROR((B51-SUMPRODUCT((SalesData[MonthNum]=$A$51)*(SalesData[Year]=$B$6-1)*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue]))/SUMPRODUCT((SalesData[MonthNum]=$A$51)*(SalesData[Year]=$B$6-1)*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue]),"n/a")))</f>
-        <v>0.58722052457269058</v>
+        <v>-0.1804386782834089</v>
       </c>
       <c r="I51" s="40">
         <f>B51*Dashboard!$AB$2</f>
-        <v>156417.44000000003</v>
+        <v>98548.020000000019</v>
       </c>
       <c r="J51" s="41">
         <f>F51*Dashboard!$AB$2</f>
-        <v>59438.630000000005</v>
+        <v>37448.239999999998</v>
       </c>
       <c r="K51" s="14"/>
       <c r="L51" s="14"/>
@@ -52469,7 +51534,7 @@
       </c>
       <c r="B52" s="11">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$52)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])</f>
-        <v>309229.51999999996</v>
+        <v>405598.20999999996</v>
       </c>
       <c r="C52" s="11">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$52)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*((SalesData[Units]&lt;&gt;0)))</f>
@@ -52477,31 +51542,31 @@
       </c>
       <c r="D52" s="11">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$52)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Units])</f>
-        <v>301</v>
+        <v>324</v>
       </c>
       <c r="E52" s="11">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$52)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Cost])</f>
-        <v>191722.31000000006</v>
+        <v>251470.88999999998</v>
       </c>
       <c r="F52" s="11">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$52)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Profit])</f>
-        <v>117507.21000000002</v>
+        <v>154127.32</v>
       </c>
       <c r="G52" s="43">
         <f t="shared" si="1"/>
-        <v>6.2925756419364515E-2</v>
+        <v>0.1227580697829378</v>
       </c>
       <c r="H52" s="43">
         <f>IF(NOT(ISNUMBER($B$6)),"n/a",IF($B$6&lt;=2022,"n/a",IFERROR((B52-SUMPRODUCT((SalesData[MonthNum]=$A$52)*(SalesData[Year]=$B$6-1)*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue]))/SUMPRODUCT((SalesData[MonthNum]=$A$52)*(SalesData[Year]=$B$6-1)*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue]),"n/a")))</f>
-        <v>-0.2375964381105134</v>
+        <v>-0.49502645551391899</v>
       </c>
       <c r="I52" s="44">
         <f>B52*Dashboard!$AB$2</f>
-        <v>309229.51999999996</v>
+        <v>405598.20999999996</v>
       </c>
       <c r="J52" s="45">
         <f>F52*Dashboard!$AB$2</f>
-        <v>117507.21000000002</v>
+        <v>154127.32</v>
       </c>
       <c r="K52" s="14"/>
       <c r="L52" s="14"/>
@@ -52521,7 +51586,7 @@
       </c>
       <c r="B53" s="47">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$53)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])</f>
-        <v>931831.9500000003</v>
+        <v>341333.08</v>
       </c>
       <c r="C53" s="47">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$53)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*((SalesData[Units]&lt;&gt;0)))</f>
@@ -52529,31 +51594,31 @@
       </c>
       <c r="D53" s="47">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$53)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Units])</f>
-        <v>540</v>
+        <v>327</v>
       </c>
       <c r="E53" s="47">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$53)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Cost])</f>
-        <v>577735.81000000006</v>
+        <v>211626.52999999997</v>
       </c>
       <c r="F53" s="47">
         <f>SUMPRODUCT((SalesData[MonthNum]=$A$53)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Profit])</f>
-        <v>354096.13999999996</v>
+        <v>129706.55</v>
       </c>
       <c r="G53" s="48">
         <f t="shared" si="1"/>
-        <v>0.18962041628328849</v>
+        <v>0.1033076306078005</v>
       </c>
       <c r="H53" s="48">
         <f>IF(NOT(ISNUMBER($B$6)),"n/a",IF($B$6&lt;=2022,"n/a",IFERROR((B53-SUMPRODUCT((SalesData[MonthNum]=$A$53)*(SalesData[Year]=$B$6-1)*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue]))/SUMPRODUCT((SalesData[MonthNum]=$A$53)*(SalesData[Year]=$B$6-1)*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue]),"n/a")))</f>
-        <v>1.729978442171501</v>
+        <v>0.4001980351870576</v>
       </c>
       <c r="I53" s="49">
         <f>B53*Dashboard!$AB$2</f>
-        <v>931831.9500000003</v>
+        <v>341333.08</v>
       </c>
       <c r="J53" s="50">
         <f>F53*Dashboard!$AB$2</f>
-        <v>354096.13999999996</v>
+        <v>129706.55</v>
       </c>
       <c r="K53" s="14"/>
       <c r="L53" s="14"/>
@@ -52573,7 +51638,7 @@
       </c>
       <c r="B54" s="52">
         <f>SUM(B42:B53)</f>
-        <v>4914196.3100000005</v>
+        <v>3304045.19</v>
       </c>
       <c r="C54" s="52">
         <f>SUM(C42:C53)</f>
@@ -52581,15 +51646,15 @@
       </c>
       <c r="D54" s="52">
         <f>SUM(D42:D53)</f>
-        <v>3831</v>
+        <v>2780</v>
       </c>
       <c r="E54" s="52">
         <f>SUM(E42:E53)</f>
-        <v>3046801.69</v>
+        <v>2048508.0999999996</v>
       </c>
       <c r="F54" s="52">
         <f>SUM(F42:F53)</f>
-        <v>1867394.6199999999</v>
+        <v>1255537.0900000001</v>
       </c>
       <c r="G54" s="53" t="s">
         <v>110</v>
@@ -52599,11 +51664,11 @@
       </c>
       <c r="I54" s="52">
         <f>SUM(I42:I53)</f>
-        <v>4914196.3100000005</v>
+        <v>3304045.19</v>
       </c>
       <c r="J54" s="54">
         <f>SUM(J42:J53)</f>
-        <v>1867394.6199999999</v>
+        <v>1255537.0900000001</v>
       </c>
       <c r="K54" s="14"/>
       <c r="L54" s="14"/>
@@ -52708,7 +51773,7 @@
       </c>
       <c r="B58" s="33">
         <f>SUMPRODUCT((SalesData[Quarter]=$A$58)*(($B$6="All")+(SalesData[Year]=$B$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])</f>
-        <v>1258730.3799999999</v>
+        <v>618550.83999999973</v>
       </c>
       <c r="C58" s="33">
         <f>SUMPRODUCT((SalesData[Quarter]=$A$58)*(($B$6="All")+(SalesData[Year]=$B$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*((SalesData[Units]&lt;&gt;0)))</f>
@@ -52716,19 +51781,19 @@
       </c>
       <c r="D58" s="33">
         <f>SUMPRODUCT((SalesData[Quarter]=$A$58)*(($B$6="All")+(SalesData[Year]=$B$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Units])</f>
-        <v>866</v>
+        <v>584</v>
       </c>
       <c r="E58" s="33">
         <f>SUMPRODUCT((SalesData[Quarter]=$A$58)*(($B$6="All")+(SalesData[Year]=$B$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Profit])</f>
-        <v>478317.53999999992</v>
+        <v>235049.30999999997</v>
       </c>
       <c r="F58" s="34">
         <f>IFERROR(B58/SUM($B$58:$B$61),0)</f>
-        <v>0.25614165584687432</v>
+        <v>0.18721016342999833</v>
       </c>
       <c r="G58" s="36">
         <f>B58*Dashboard!$AB$2</f>
-        <v>1258730.3799999999</v>
+        <v>618550.83999999973</v>
       </c>
       <c r="H58" s="14"/>
       <c r="I58" s="14"/>
@@ -52751,7 +51816,7 @@
       </c>
       <c r="B59" s="11">
         <f>SUMPRODUCT((SalesData[Quarter]=$A$59)*(($B$6="All")+(SalesData[Year]=$B$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])</f>
-        <v>910640.34</v>
+        <v>1032234.4299999998</v>
       </c>
       <c r="C59" s="11">
         <f>SUMPRODUCT((SalesData[Quarter]=$A$59)*(($B$6="All")+(SalesData[Year]=$B$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*((SalesData[Units]&lt;&gt;0)))</f>
@@ -52759,19 +51824,19 @@
       </c>
       <c r="D59" s="11">
         <f>SUMPRODUCT((SalesData[Quarter]=$A$59)*(($B$6="All")+(SalesData[Year]=$B$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Units])</f>
-        <v>810</v>
+        <v>612</v>
       </c>
       <c r="E59" s="11">
         <f>SUMPRODUCT((SalesData[Quarter]=$A$59)*(($B$6="All")+(SalesData[Year]=$B$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Profit])</f>
-        <v>346043.3600000001</v>
+        <v>392249.04000000004</v>
       </c>
       <c r="F59" s="43">
         <f>IFERROR(B59/SUM($B$58:$B$61),0)</f>
-        <v>0.18530809160938869</v>
+        <v>0.31241534865326703</v>
       </c>
       <c r="G59" s="45">
         <f>B59*Dashboard!$AB$2</f>
-        <v>910640.34</v>
+        <v>1032234.4299999998</v>
       </c>
       <c r="H59" s="14"/>
       <c r="I59" s="14"/>
@@ -52794,7 +51859,7 @@
       </c>
       <c r="B60" s="11">
         <f>SUMPRODUCT((SalesData[Quarter]=$A$60)*(($B$6="All")+(SalesData[Year]=$B$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])</f>
-        <v>1347346.6800000002</v>
+        <v>807780.60999999975</v>
       </c>
       <c r="C60" s="11">
         <f>SUMPRODUCT((SalesData[Quarter]=$A$60)*(($B$6="All")+(SalesData[Year]=$B$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*((SalesData[Units]&lt;&gt;0)))</f>
@@ -52802,19 +51867,19 @@
       </c>
       <c r="D60" s="11">
         <f>SUMPRODUCT((SalesData[Quarter]=$A$60)*(($B$6="All")+(SalesData[Year]=$B$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Units])</f>
-        <v>1008</v>
+        <v>619</v>
       </c>
       <c r="E60" s="11">
         <f>SUMPRODUCT((SalesData[Quarter]=$A$60)*(($B$6="All")+(SalesData[Year]=$B$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Profit])</f>
-        <v>511991.73999999993</v>
+        <v>306956.63</v>
       </c>
       <c r="F60" s="43">
         <f>IFERROR(B60/SUM($B$58:$B$61),0)</f>
-        <v>0.27417437053913707</v>
+        <v>0.24448231290686429</v>
       </c>
       <c r="G60" s="45">
         <f>B60*Dashboard!$AB$2</f>
-        <v>1347346.6800000002</v>
+        <v>807780.60999999975</v>
       </c>
       <c r="H60" s="14"/>
       <c r="I60" s="14"/>
@@ -52837,7 +51902,7 @@
       </c>
       <c r="B61" s="58">
         <f>SUMPRODUCT((SalesData[Quarter]=$A$61)*(($B$6="All")+(SalesData[Year]=$B$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])</f>
-        <v>1397478.9100000001</v>
+        <v>845479.30999999994</v>
       </c>
       <c r="C61" s="58">
         <f>SUMPRODUCT((SalesData[Quarter]=$A$61)*(($B$6="All")+(SalesData[Year]=$B$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*((SalesData[Units]&lt;&gt;0)))</f>
@@ -52845,19 +51910,19 @@
       </c>
       <c r="D61" s="58">
         <f>SUMPRODUCT((SalesData[Quarter]=$A$61)*(($B$6="All")+(SalesData[Year]=$B$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Units])</f>
-        <v>1147</v>
+        <v>965</v>
       </c>
       <c r="E61" s="58">
         <f>SUMPRODUCT((SalesData[Quarter]=$A$61)*(($B$6="All")+(SalesData[Year]=$B$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Profit])</f>
-        <v>531041.9800000001</v>
+        <v>321282.11000000004</v>
       </c>
       <c r="F61" s="59">
         <f>IFERROR(B61/SUM($B$58:$B$61),0)</f>
-        <v>0.28437588200459984</v>
+        <v>0.25589217500987027</v>
       </c>
       <c r="G61" s="60">
         <f>B61*Dashboard!$AB$2</f>
-        <v>1397478.9100000001</v>
+        <v>845479.30999999994</v>
       </c>
       <c r="H61" s="14"/>
       <c r="I61" s="14"/>
@@ -52880,7 +51945,7 @@
       </c>
       <c r="B62" s="52">
         <f>SUM(B58:B61)</f>
-        <v>4914196.3100000005</v>
+        <v>3304045.1899999995</v>
       </c>
       <c r="C62" s="52">
         <f>SUM(C58:C61)</f>
@@ -52888,16 +51953,16 @@
       </c>
       <c r="D62" s="52">
         <f>SUM(D58:D61)</f>
-        <v>3831</v>
+        <v>2780</v>
       </c>
       <c r="E62" s="52">
         <f>SUM(E58:E61)</f>
-        <v>1867394.62</v>
+        <v>1255537.0900000001</v>
       </c>
       <c r="F62" s="61"/>
       <c r="G62" s="54">
         <f>SUM(G58:G61)</f>
-        <v>4914196.3100000005</v>
+        <v>3304045.1899999995</v>
       </c>
       <c r="H62" s="14"/>
       <c r="I62" s="14"/>
@@ -53003,23 +52068,23 @@
       </c>
       <c r="B66" s="33">
         <f>SUMPRODUCT((SalesData[Region]=$A$66)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])</f>
-        <v>644006.04000000015</v>
+        <v>1091350.9099999999</v>
       </c>
       <c r="C66" s="33">
         <f>SUMPRODUCT((SalesData[Region]=$A$66)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*((SalesData[Units]&lt;&gt;0)))</f>
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="D66" s="33">
         <f>SUMPRODUCT((SalesData[Region]=$A$66)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Units])</f>
-        <v>620</v>
+        <v>757</v>
       </c>
       <c r="E66" s="34">
         <f>IFERROR(B66/SUM($B$66:$B$70),0)</f>
-        <v>0.13105012485754772</v>
+        <v>0.33030750103027495</v>
       </c>
       <c r="F66" s="36">
         <f>B66*Dashboard!$AB$2</f>
-        <v>644006.04000000015</v>
+        <v>1091350.9099999999</v>
       </c>
       <c r="G66" s="14"/>
       <c r="H66" s="14"/>
@@ -53043,23 +52108,23 @@
       </c>
       <c r="B67" s="11">
         <f>SUMPRODUCT((SalesData[Region]=$A$67)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])</f>
-        <v>1432864.93</v>
+        <v>576134.40999999992</v>
       </c>
       <c r="C67" s="11">
         <f>SUMPRODUCT((SalesData[Region]=$A$67)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*((SalesData[Units]&lt;&gt;0)))</f>
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="D67" s="11">
         <f>SUMPRODUCT((SalesData[Region]=$A$67)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Units])</f>
-        <v>804</v>
+        <v>445</v>
       </c>
       <c r="E67" s="43">
         <f>IFERROR(B67/SUM($B$66:$B$70),0)</f>
-        <v>0.29157665661101767</v>
+        <v>0.17437243647384859</v>
       </c>
       <c r="F67" s="45">
         <f>B67*Dashboard!$AB$2</f>
-        <v>1432864.93</v>
+        <v>576134.40999999992</v>
       </c>
       <c r="G67" s="14"/>
       <c r="H67" s="14"/>
@@ -53083,23 +52148,23 @@
       </c>
       <c r="B68" s="11">
         <f>SUMPRODUCT((SalesData[Region]=$A$68)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])</f>
-        <v>837545.24</v>
+        <v>542262.50999999978</v>
       </c>
       <c r="C68" s="11">
         <f>SUMPRODUCT((SalesData[Region]=$A$68)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*((SalesData[Units]&lt;&gt;0)))</f>
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D68" s="11">
         <f>SUMPRODUCT((SalesData[Region]=$A$68)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Units])</f>
-        <v>667</v>
+        <v>503</v>
       </c>
       <c r="E68" s="43">
         <f>IFERROR(B68/SUM($B$66:$B$70),0)</f>
-        <v>0.17043381809873201</v>
+        <v>0.16412079097501686</v>
       </c>
       <c r="F68" s="45">
         <f>B68*Dashboard!$AB$2</f>
-        <v>837545.24</v>
+        <v>542262.50999999978</v>
       </c>
       <c r="G68" s="14"/>
       <c r="H68" s="14"/>
@@ -53123,23 +52188,23 @@
       </c>
       <c r="B69" s="11">
         <f>SUMPRODUCT((SalesData[Region]=$A$69)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])</f>
-        <v>1083542.3099999998</v>
+        <v>610033.9</v>
       </c>
       <c r="C69" s="11">
         <f>SUMPRODUCT((SalesData[Region]=$A$69)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*((SalesData[Units]&lt;&gt;0)))</f>
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="D69" s="11">
         <f>SUMPRODUCT((SalesData[Region]=$A$69)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Units])</f>
-        <v>1005</v>
+        <v>512</v>
       </c>
       <c r="E69" s="43">
         <f>IFERROR(B69/SUM($B$66:$B$70),0)</f>
-        <v>0.22049227211275163</v>
+        <v>0.1846324323427308</v>
       </c>
       <c r="F69" s="45">
         <f>B69*Dashboard!$AB$2</f>
-        <v>1083542.3099999998</v>
+        <v>610033.9</v>
       </c>
       <c r="G69" s="14"/>
       <c r="H69" s="14"/>
@@ -53163,23 +52228,23 @@
       </c>
       <c r="B70" s="58">
         <f>SUMPRODUCT((SalesData[Region]=$A$70)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])</f>
-        <v>916237.7899999998</v>
+        <v>484263.4599999999</v>
       </c>
       <c r="C70" s="58">
         <f>SUMPRODUCT((SalesData[Region]=$A$70)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*((SalesData[Units]&lt;&gt;0)))</f>
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D70" s="58">
         <f>SUMPRODUCT((SalesData[Region]=$A$70)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Units])</f>
-        <v>735</v>
+        <v>563</v>
       </c>
       <c r="E70" s="59">
         <f>IFERROR(B70/SUM($B$66:$B$70),0)</f>
-        <v>0.18644712831995103</v>
+        <v>0.14656683917812879</v>
       </c>
       <c r="F70" s="60">
         <f>B70*Dashboard!$AB$2</f>
-        <v>916237.7899999998</v>
+        <v>484263.4599999999</v>
       </c>
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
@@ -53203,14 +52268,14 @@
       </c>
       <c r="B71" s="52">
         <f>SUM(B66:B70)</f>
-        <v>4914196.3099999996</v>
+        <v>3304045.1899999995</v>
       </c>
       <c r="C71" s="61"/>
       <c r="D71" s="61"/>
       <c r="E71" s="61"/>
       <c r="F71" s="54">
         <f>SUM(F66:F70)</f>
-        <v>4914196.3099999996</v>
+        <v>3304045.1899999995</v>
       </c>
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
@@ -53317,23 +52382,23 @@
       </c>
       <c r="B75" s="33">
         <f>SUMPRODUCT((SalesData[Category]=$A$75)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])</f>
-        <v>83951.659999999974</v>
+        <v>47001.42000000002</v>
       </c>
       <c r="C75" s="33">
         <f>SUMPRODUCT((SalesData[Category]=$A$75)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Profit])</f>
-        <v>31901.65</v>
+        <v>17860.530000000002</v>
       </c>
       <c r="D75" s="34">
         <f>IFERROR(C75/B75,0)</f>
-        <v>0.38000022870304184</v>
+        <v>0.37999979575085169</v>
       </c>
       <c r="E75" s="34">
         <f>IFERROR(B75/SUM($B$75:$B$79),0)</f>
-        <v>1.7083497423406754E-2</v>
+        <v>1.4225416813987346E-2</v>
       </c>
       <c r="F75" s="36">
         <f>B75*Dashboard!$AB$2</f>
-        <v>83951.659999999974</v>
+        <v>47001.42000000002</v>
       </c>
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
@@ -53357,23 +52422,23 @@
       </c>
       <c r="B76" s="11">
         <f>SUMPRODUCT((SalesData[Category]=$A$76)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])</f>
-        <v>2004450.33</v>
+        <v>1213707.4200000002</v>
       </c>
       <c r="C76" s="11">
         <f>SUMPRODUCT((SalesData[Category]=$A$76)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Profit])</f>
-        <v>761691.1399999999</v>
+        <v>461208.77</v>
       </c>
       <c r="D76" s="43">
         <f>IFERROR(C76/B76,0)</f>
-        <v>0.3800000072837923</v>
+        <v>0.37999995913347878</v>
       </c>
       <c r="E76" s="43">
         <f>IFERROR(B76/SUM($B$75:$B$79),0)</f>
-        <v>0.40788975522225329</v>
+        <v>0.36733983653534713</v>
       </c>
       <c r="F76" s="45">
         <f>B76*Dashboard!$AB$2</f>
-        <v>2004450.33</v>
+        <v>1213707.4200000002</v>
       </c>
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
@@ -53397,23 +52462,23 @@
       </c>
       <c r="B77" s="11">
         <f>SUMPRODUCT((SalesData[Category]=$A$77)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])</f>
-        <v>216590.40999999997</v>
+        <v>183824.42</v>
       </c>
       <c r="C77" s="11">
         <f>SUMPRODUCT((SalesData[Category]=$A$77)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Profit])</f>
-        <v>82304.36</v>
+        <v>69853.27</v>
       </c>
       <c r="D77" s="43">
         <f>IFERROR(C77/B77,0)</f>
-        <v>0.38000001939144035</v>
+        <v>0.37999994777625301</v>
       </c>
       <c r="E77" s="43">
         <f>IFERROR(B77/SUM($B$75:$B$79),0)</f>
-        <v>4.407443177621042E-2</v>
+        <v>5.5636170036766353E-2</v>
       </c>
       <c r="F77" s="45">
         <f>B77*Dashboard!$AB$2</f>
-        <v>216590.40999999997</v>
+        <v>183824.42</v>
       </c>
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
@@ -53437,23 +52502,23 @@
       </c>
       <c r="B78" s="11">
         <f>SUMPRODUCT((SalesData[Category]=$A$78)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])</f>
-        <v>171530.68999999994</v>
+        <v>129765.93000000001</v>
       </c>
       <c r="C78" s="11">
         <f>SUMPRODUCT((SalesData[Category]=$A$78)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Profit])</f>
-        <v>65181.65</v>
+        <v>49311.05000000001</v>
       </c>
       <c r="D78" s="43">
         <f>IFERROR(C78/B78,0)</f>
-        <v>0.37999992887570161</v>
+        <v>0.37999997379897793</v>
       </c>
       <c r="E78" s="43">
         <f>IFERROR(B78/SUM($B$75:$B$79),0)</f>
-        <v>3.49051358918952E-2</v>
+        <v>3.9274865365869889E-2</v>
       </c>
       <c r="F78" s="45">
         <f>B78*Dashboard!$AB$2</f>
-        <v>171530.68999999994</v>
+        <v>129765.93000000001</v>
       </c>
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
@@ -53477,23 +52542,23 @@
       </c>
       <c r="B79" s="58">
         <f>SUMPRODUCT((SalesData[Category]=$A$79)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])</f>
-        <v>2437673.2199999997</v>
+        <v>1729746.0000000002</v>
       </c>
       <c r="C79" s="58">
         <f>SUMPRODUCT((SalesData[Category]=$A$79)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Profit])</f>
-        <v>926315.82000000007</v>
+        <v>657303.47</v>
       </c>
       <c r="D79" s="59">
         <f>IFERROR(C79/B79,0)</f>
-        <v>0.37999999852318195</v>
+        <v>0.37999999421880432</v>
       </c>
       <c r="E79" s="59">
         <f>IFERROR(B79/SUM($B$75:$B$79),0)</f>
-        <v>0.49604717968623435</v>
+        <v>0.52352371124802932</v>
       </c>
       <c r="F79" s="60">
         <f>B79*Dashboard!$AB$2</f>
-        <v>2437673.2199999997</v>
+        <v>1729746.0000000002</v>
       </c>
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
@@ -53517,17 +52582,17 @@
       </c>
       <c r="B80" s="52">
         <f>SUM(B75:B79)</f>
-        <v>4914196.3099999996</v>
+        <v>3304045.1900000004</v>
       </c>
       <c r="C80" s="52">
         <f>SUM(C75:C79)</f>
-        <v>1867394.62</v>
+        <v>1255537.0900000001</v>
       </c>
       <c r="D80" s="61"/>
       <c r="E80" s="61"/>
       <c r="F80" s="54">
         <f>SUM(F75:F79)</f>
-        <v>4914196.3099999996</v>
+        <v>3304045.1900000004</v>
       </c>
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
@@ -53634,23 +52699,23 @@
       </c>
       <c r="B84" s="33">
         <f>SUMPRODUCT((SalesData[Salesperson]=$A$84)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])</f>
-        <v>873158.79</v>
+        <v>539907.66999999993</v>
       </c>
       <c r="C84" s="33">
         <f>SUMPRODUCT((SalesData[Salesperson]=$A$84)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($H$6="All")+(SalesData[Product]=$H$6))*((SalesData[Units]&lt;&gt;0)))</f>
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D84" s="33">
         <f>SUMPRODUCT((SalesData[Salesperson]=$A$84)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Units])</f>
-        <v>710</v>
+        <v>560</v>
       </c>
       <c r="E84" s="34">
         <f t="shared" ref="E84:E89" si="2">IFERROR(B84/SUM($B$84:$B$89),0)</f>
-        <v>0.17768089325678565</v>
+        <v>0.16340807675212216</v>
       </c>
       <c r="F84" s="36">
         <f>B84*Dashboard!$AB$2</f>
-        <v>873158.79</v>
+        <v>539907.66999999993</v>
       </c>
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
@@ -53674,23 +52739,23 @@
       </c>
       <c r="B85" s="11">
         <f>SUMPRODUCT((SalesData[Salesperson]=$A$85)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])</f>
-        <v>677603.15000000014</v>
+        <v>517561.36</v>
       </c>
       <c r="C85" s="11">
         <f>SUMPRODUCT((SalesData[Salesperson]=$A$85)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($H$6="All")+(SalesData[Product]=$H$6))*((SalesData[Units]&lt;&gt;0)))</f>
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D85" s="11">
         <f>SUMPRODUCT((SalesData[Salesperson]=$A$85)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Units])</f>
-        <v>509</v>
+        <v>452</v>
       </c>
       <c r="E85" s="43">
         <f t="shared" si="2"/>
-        <v>0.13788687045756218</v>
+        <v>0.15664475823952034</v>
       </c>
       <c r="F85" s="45">
         <f>B85*Dashboard!$AB$2</f>
-        <v>677603.15000000014</v>
+        <v>517561.36</v>
       </c>
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
@@ -53714,23 +52779,23 @@
       </c>
       <c r="B86" s="11">
         <f>SUMPRODUCT((SalesData[Salesperson]=$A$86)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])</f>
-        <v>635295.81000000006</v>
+        <v>559937.65999999992</v>
       </c>
       <c r="C86" s="11">
         <f>SUMPRODUCT((SalesData[Salesperson]=$A$86)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($H$6="All")+(SalesData[Product]=$H$6))*((SalesData[Units]&lt;&gt;0)))</f>
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D86" s="11">
         <f>SUMPRODUCT((SalesData[Salesperson]=$A$86)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Units])</f>
-        <v>645</v>
+        <v>325</v>
       </c>
       <c r="E86" s="43">
         <f t="shared" si="2"/>
-        <v>0.12927766208835073</v>
+        <v>0.16947033947801424</v>
       </c>
       <c r="F86" s="45">
         <f>B86*Dashboard!$AB$2</f>
-        <v>635295.81000000006</v>
+        <v>559937.65999999992</v>
       </c>
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
@@ -53754,23 +52819,23 @@
       </c>
       <c r="B87" s="11">
         <f>SUMPRODUCT((SalesData[Salesperson]=$A$87)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])</f>
-        <v>631248.94999999995</v>
+        <v>441005.19999999984</v>
       </c>
       <c r="C87" s="11">
         <f>SUMPRODUCT((SalesData[Salesperson]=$A$87)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($H$6="All")+(SalesData[Product]=$H$6))*((SalesData[Units]&lt;&gt;0)))</f>
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D87" s="11">
         <f>SUMPRODUCT((SalesData[Salesperson]=$A$87)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Units])</f>
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="E87" s="43">
         <f t="shared" si="2"/>
-        <v>0.12845415815307548</v>
+        <v>0.13347432454457436</v>
       </c>
       <c r="F87" s="45">
         <f>B87*Dashboard!$AB$2</f>
-        <v>631248.94999999995</v>
+        <v>441005.19999999984</v>
       </c>
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
@@ -53794,23 +52859,23 @@
       </c>
       <c r="B88" s="11">
         <f>SUMPRODUCT((SalesData[Salesperson]=$A$88)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])</f>
-        <v>761218.98</v>
+        <v>747025.21</v>
       </c>
       <c r="C88" s="11">
         <f>SUMPRODUCT((SalesData[Salesperson]=$A$88)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($H$6="All")+(SalesData[Product]=$H$6))*((SalesData[Units]&lt;&gt;0)))</f>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D88" s="11">
         <f>SUMPRODUCT((SalesData[Salesperson]=$A$88)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Units])</f>
-        <v>547</v>
+        <v>432</v>
       </c>
       <c r="E88" s="43">
         <f t="shared" si="2"/>
-        <v>0.15490202913770043</v>
+        <v>0.22609412615207</v>
       </c>
       <c r="F88" s="45">
         <f>B88*Dashboard!$AB$2</f>
-        <v>761218.98</v>
+        <v>747025.21</v>
       </c>
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
@@ -53834,23 +52899,23 @@
       </c>
       <c r="B89" s="58">
         <f>SUMPRODUCT((SalesData[Salesperson]=$A$89)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])</f>
-        <v>1335670.6299999999</v>
+        <v>498608.08999999991</v>
       </c>
       <c r="C89" s="58">
         <f>SUMPRODUCT((SalesData[Salesperson]=$A$89)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($H$6="All")+(SalesData[Product]=$H$6))*((SalesData[Units]&lt;&gt;0)))</f>
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D89" s="58">
         <f>SUMPRODUCT((SalesData[Salesperson]=$A$89)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Units])</f>
-        <v>921</v>
+        <v>519</v>
       </c>
       <c r="E89" s="59">
         <f t="shared" si="2"/>
-        <v>0.27179838690652547</v>
+        <v>0.15090837483369893</v>
       </c>
       <c r="F89" s="60">
         <f>B89*Dashboard!$AB$2</f>
-        <v>1335670.6299999999</v>
+        <v>498608.08999999991</v>
       </c>
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
@@ -53874,14 +52939,14 @@
       </c>
       <c r="B90" s="52">
         <f>SUM(B84:B89)</f>
-        <v>4914196.3100000005</v>
+        <v>3304045.1899999995</v>
       </c>
       <c r="C90" s="61"/>
       <c r="D90" s="61"/>
       <c r="E90" s="61"/>
       <c r="F90" s="54">
         <f>SUM(F84:F89)</f>
-        <v>4914196.3100000005</v>
+        <v>3304045.1899999995</v>
       </c>
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
@@ -53986,19 +53051,19 @@
       </c>
       <c r="B94" s="33">
         <f>SUMPRODUCT((SalesData[Product]=$A$94)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Revenue])</f>
-        <v>425258.29000000004</v>
+        <v>59779.59</v>
       </c>
       <c r="C94" s="33">
         <f>SUMPRODUCT((SalesData[Product]=$A$94)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Profit])</f>
-        <v>161598.15000000002</v>
+        <v>22716.239999999998</v>
       </c>
       <c r="D94" s="33">
         <f>SUMPRODUCT((SalesData[Product]=$A$94)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Units])</f>
-        <v>176</v>
+        <v>31</v>
       </c>
       <c r="E94" s="62">
         <f t="shared" ref="E94:E118" si="3">IFERROR(C94/B94,0)</f>
-        <v>0.3799999995296976</v>
+        <v>0.37999992974190688</v>
       </c>
       <c r="F94" s="14"/>
       <c r="G94" s="14"/>
@@ -54023,19 +53088,19 @@
       </c>
       <c r="B95" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$95)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Revenue])</f>
-        <v>20697.680000000004</v>
+        <v>7452.74</v>
       </c>
       <c r="C95" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$95)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Profit])</f>
-        <v>7865.1200000000008</v>
+        <v>2832.04</v>
       </c>
       <c r="D95" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$95)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Units])</f>
-        <v>208</v>
+        <v>87</v>
       </c>
       <c r="E95" s="63">
         <f t="shared" si="3"/>
-        <v>0.38000007730334989</v>
+        <v>0.3799998389853933</v>
       </c>
       <c r="F95" s="14"/>
       <c r="G95" s="14"/>
@@ -54060,19 +53125,19 @@
       </c>
       <c r="B96" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$96)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Revenue])</f>
-        <v>13501.26</v>
+        <v>7655.5300000000007</v>
       </c>
       <c r="C96" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$96)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Profit])</f>
-        <v>5130.49</v>
+        <v>2909.09</v>
       </c>
       <c r="D96" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$96)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Units])</f>
-        <v>162</v>
+        <v>99</v>
       </c>
       <c r="E96" s="63">
         <f t="shared" si="3"/>
-        <v>0.38000082955220471</v>
+        <v>0.37999851088037012</v>
       </c>
       <c r="F96" s="14"/>
       <c r="G96" s="14"/>
@@ -54097,19 +53162,19 @@
       </c>
       <c r="B97" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$97)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Revenue])</f>
-        <v>548078.28</v>
+        <v>294378.95</v>
       </c>
       <c r="C97" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$97)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Profit])</f>
-        <v>208269.75</v>
+        <v>111863.99</v>
       </c>
       <c r="D97" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$97)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Units])</f>
-        <v>185</v>
+        <v>159</v>
       </c>
       <c r="E97" s="63">
         <f t="shared" si="3"/>
-        <v>0.38000000656840477</v>
+        <v>0.3799999626331978</v>
       </c>
       <c r="F97" s="14"/>
       <c r="G97" s="14"/>
@@ -54134,19 +53199,19 @@
       </c>
       <c r="B98" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$98)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Revenue])</f>
-        <v>28937.8</v>
+        <v>22220.54</v>
       </c>
       <c r="C98" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$98)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Profit])</f>
-        <v>10996.359999999999</v>
+        <v>8443.8000000000011</v>
       </c>
       <c r="D98" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$98)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Units])</f>
-        <v>104</v>
+        <v>66</v>
       </c>
       <c r="E98" s="63">
         <f t="shared" si="3"/>
-        <v>0.37999986177249129</v>
+        <v>0.37999976598228491</v>
       </c>
       <c r="F98" s="14"/>
       <c r="G98" s="14"/>
@@ -54171,19 +53236,19 @@
       </c>
       <c r="B99" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$99)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Revenue])</f>
-        <v>123282.81</v>
+        <v>477858.96</v>
       </c>
       <c r="C99" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$99)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Profit])</f>
-        <v>46847.47</v>
+        <v>181586.38</v>
       </c>
       <c r="D99" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$99)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Units])</f>
-        <v>54</v>
+        <v>225</v>
       </c>
       <c r="E99" s="63">
         <f t="shared" si="3"/>
-        <v>0.38000001784514809</v>
+        <v>0.37999994810184157</v>
       </c>
       <c r="F99" s="14"/>
       <c r="G99" s="14"/>
@@ -54208,19 +53273,19 @@
       </c>
       <c r="B100" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$100)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Revenue])</f>
-        <v>18173.059999999998</v>
+        <v>21927.32</v>
       </c>
       <c r="C100" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$100)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Profit])</f>
-        <v>6905.7599999999993</v>
+        <v>8332.39</v>
       </c>
       <c r="D100" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$100)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Units])</f>
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E100" s="63">
         <f t="shared" si="3"/>
-        <v>0.37999984592578245</v>
+        <v>0.38000038308375123</v>
       </c>
       <c r="F100" s="14"/>
       <c r="G100" s="14"/>
@@ -54245,19 +53310,19 @@
       </c>
       <c r="B101" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$101)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Revenue])</f>
-        <v>759688.02</v>
+        <v>281950.75</v>
       </c>
       <c r="C101" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$101)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Profit])</f>
-        <v>288681.45</v>
+        <v>107141.28</v>
       </c>
       <c r="D101" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$101)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Units])</f>
-        <v>187</v>
+        <v>132</v>
       </c>
       <c r="E101" s="63">
         <f t="shared" si="3"/>
-        <v>0.38000000315919158</v>
+        <v>0.37999998226640647</v>
       </c>
       <c r="F101" s="14"/>
       <c r="G101" s="14"/>
@@ -54282,19 +53347,19 @@
       </c>
       <c r="B102" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$102)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Revenue])</f>
-        <v>43270.61</v>
+        <v>32289.57</v>
       </c>
       <c r="C102" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$102)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Profit])</f>
-        <v>16442.830000000002</v>
+        <v>12270.03</v>
       </c>
       <c r="D102" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$102)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Units])</f>
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="E102" s="63">
         <f t="shared" si="3"/>
-        <v>0.379999958401326</v>
+        <v>0.37999979559963171</v>
       </c>
       <c r="F102" s="14"/>
       <c r="G102" s="14"/>
@@ -54319,19 +53384,19 @@
       </c>
       <c r="B103" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$103)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Revenue])</f>
-        <v>38812.11</v>
+        <v>14581.87</v>
       </c>
       <c r="C103" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$103)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Profit])</f>
-        <v>14748.619999999999</v>
+        <v>5541.1100000000006</v>
       </c>
       <c r="D103" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$103)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Units])</f>
-        <v>138</v>
+        <v>70</v>
       </c>
       <c r="E103" s="63">
         <f t="shared" si="3"/>
-        <v>0.38000046892580691</v>
+        <v>0.37999995885301407</v>
       </c>
       <c r="F103" s="14"/>
       <c r="G103" s="14"/>
@@ -54356,19 +53421,19 @@
       </c>
       <c r="B104" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$104)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Revenue])</f>
-        <v>360465.91999999998</v>
+        <v>556108.1</v>
       </c>
       <c r="C104" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$104)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Profit])</f>
-        <v>136977.04999999999</v>
+        <v>211321.08</v>
       </c>
       <c r="D104" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$104)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Units])</f>
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="E104" s="63">
         <f t="shared" si="3"/>
-        <v>0.38000000110967491</v>
+        <v>0.38000000359642305</v>
       </c>
       <c r="F104" s="14"/>
       <c r="G104" s="14"/>
@@ -54393,19 +53458,19 @@
       </c>
       <c r="B105" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$105)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Revenue])</f>
-        <v>435057.76999999996</v>
+        <v>298699.01</v>
       </c>
       <c r="C105" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$105)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Profit])</f>
-        <v>165321.95000000001</v>
+        <v>113505.62</v>
       </c>
       <c r="D105" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$105)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Units])</f>
-        <v>132</v>
+        <v>93</v>
       </c>
       <c r="E105" s="63">
         <f t="shared" si="3"/>
-        <v>0.37999999402378226</v>
+        <v>0.37999998727816336</v>
       </c>
       <c r="F105" s="14"/>
       <c r="G105" s="14"/>
@@ -54430,19 +53495,19 @@
       </c>
       <c r="B106" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$106)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Revenue])</f>
-        <v>216559.27999999997</v>
+        <v>169379.5</v>
       </c>
       <c r="C106" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$106)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Profit])</f>
-        <v>82292.529999999984</v>
+        <v>64364.2</v>
       </c>
       <c r="D106" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$106)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Units])</f>
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="E106" s="63">
         <f t="shared" si="3"/>
-        <v>0.38000001662362376</v>
+        <v>0.37999994096097817</v>
       </c>
       <c r="F106" s="14"/>
       <c r="G106" s="14"/>
@@ -54467,19 +53532,19 @@
       </c>
       <c r="B107" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$107)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Revenue])</f>
-        <v>12560.67</v>
+        <v>11141.54</v>
       </c>
       <c r="C107" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$107)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Profit])</f>
-        <v>4773.05</v>
+        <v>4233.79</v>
       </c>
       <c r="D107" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$107)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Units])</f>
-        <v>175</v>
+        <v>111</v>
       </c>
       <c r="E107" s="63">
         <f t="shared" si="3"/>
-        <v>0.37999963377749757</v>
+        <v>0.38000043082015589</v>
       </c>
       <c r="F107" s="14"/>
       <c r="G107" s="14"/>
@@ -54504,19 +53569,19 @@
       </c>
       <c r="B108" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$108)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Revenue])</f>
-        <v>471256.17000000004</v>
+        <v>381998.4</v>
       </c>
       <c r="C108" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$108)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Profit])</f>
-        <v>179077.34</v>
+        <v>145159.38999999998</v>
       </c>
       <c r="D108" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$108)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Units])</f>
-        <v>177</v>
+        <v>76</v>
       </c>
       <c r="E108" s="63">
         <f t="shared" si="3"/>
-        <v>0.37999999023885456</v>
+        <v>0.3799999947643759</v>
       </c>
       <c r="F108" s="14"/>
       <c r="G108" s="14"/>
@@ -54541,19 +53606,19 @@
       </c>
       <c r="B109" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$109)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Revenue])</f>
-        <v>67267.45</v>
+        <v>33704.57</v>
       </c>
       <c r="C109" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$109)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Profit])</f>
-        <v>25561.61</v>
+        <v>12807.74</v>
       </c>
       <c r="D109" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$109)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Units])</f>
-        <v>206</v>
+        <v>126</v>
       </c>
       <c r="E109" s="63">
         <f t="shared" si="3"/>
-        <v>0.37999968781334809</v>
+        <v>0.38000010087652802</v>
       </c>
       <c r="F109" s="14"/>
       <c r="G109" s="14"/>
@@ -54578,19 +53643,19 @@
       </c>
       <c r="B110" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$110)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Revenue])</f>
-        <v>691271.67</v>
+        <v>212310.41999999998</v>
       </c>
       <c r="C110" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$110)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Profit])</f>
-        <v>262683.24</v>
+        <v>80677.959999999992</v>
       </c>
       <c r="D110" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$110)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Units])</f>
-        <v>244</v>
+        <v>70</v>
       </c>
       <c r="E110" s="63">
         <f t="shared" si="3"/>
-        <v>0.38000000781168997</v>
+        <v>0.38000000188403377</v>
       </c>
       <c r="F110" s="14"/>
       <c r="G110" s="14"/>
@@ -54615,19 +53680,19 @@
       </c>
       <c r="B111" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$111)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Revenue])</f>
-        <v>16936.25</v>
+        <v>8217.7199999999993</v>
       </c>
       <c r="C111" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$111)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Profit])</f>
-        <v>6435.7899999999991</v>
+        <v>3122.7299999999996</v>
       </c>
       <c r="D111" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$111)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Units])</f>
-        <v>207</v>
+        <v>114</v>
       </c>
       <c r="E111" s="63">
         <f t="shared" si="3"/>
-        <v>0.38000088567421947</v>
+        <v>0.37999956192228501</v>
       </c>
       <c r="F111" s="14"/>
       <c r="G111" s="14"/>
@@ -54652,19 +53717,19 @@
       </c>
       <c r="B112" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$112)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Revenue])</f>
-        <v>59692.89</v>
+        <v>68513.939999999988</v>
       </c>
       <c r="C112" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$112)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Profit])</f>
-        <v>22683.3</v>
+        <v>26035.29</v>
       </c>
       <c r="D112" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$112)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Units])</f>
-        <v>237</v>
+        <v>202</v>
       </c>
       <c r="E112" s="63">
         <f t="shared" si="3"/>
-        <v>0.38000003015434503</v>
+        <v>0.37999989491189684</v>
       </c>
       <c r="F112" s="14"/>
       <c r="G112" s="14"/>
@@ -54689,19 +53754,19 @@
       </c>
       <c r="B113" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$113)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Revenue])</f>
-        <v>7547.35</v>
+        <v>34734.47</v>
       </c>
       <c r="C113" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$113)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Profit])</f>
-        <v>2868</v>
+        <v>13199.099999999999</v>
       </c>
       <c r="D113" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$113)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Units])</f>
-        <v>20</v>
+        <v>128</v>
       </c>
       <c r="E113" s="63">
         <f t="shared" si="3"/>
-        <v>0.38000092747785646</v>
+        <v>0.38000004030578266</v>
       </c>
       <c r="F113" s="14"/>
       <c r="G113" s="14"/>
@@ -54726,19 +53791,19 @@
       </c>
       <c r="B114" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$114)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Revenue])</f>
-        <v>411205.34</v>
+        <v>210989.74</v>
       </c>
       <c r="C114" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$114)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Profit])</f>
-        <v>156258.02999999997</v>
+        <v>80176.100000000006</v>
       </c>
       <c r="D114" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$114)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Units])</f>
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="E114" s="63">
         <f t="shared" si="3"/>
-        <v>0.38000000194549993</v>
+        <v>0.37999999431251968</v>
       </c>
       <c r="F114" s="14"/>
       <c r="G114" s="14"/>
@@ -54763,19 +53828,19 @@
       </c>
       <c r="B115" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$115)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Revenue])</f>
-        <v>20255.8</v>
+        <v>12533.89</v>
       </c>
       <c r="C115" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$115)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Profit])</f>
-        <v>7697.2000000000007</v>
+        <v>4762.88</v>
       </c>
       <c r="D115" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$115)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Units])</f>
-        <v>216</v>
+        <v>132</v>
       </c>
       <c r="E115" s="63">
         <f t="shared" si="3"/>
-        <v>0.37999980252569637</v>
+        <v>0.38000014361064283</v>
       </c>
       <c r="F115" s="14"/>
       <c r="G115" s="14"/>
@@ -54800,19 +53865,19 @@
       </c>
       <c r="B116" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$116)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Revenue])</f>
-        <v>21346.499999999996</v>
+        <v>24627.329999999998</v>
       </c>
       <c r="C116" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$116)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Profit])</f>
-        <v>8111.67</v>
+        <v>9358.380000000001</v>
       </c>
       <c r="D116" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$116)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Units])</f>
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="E116" s="63">
         <f t="shared" si="3"/>
-        <v>0.38000000000000006</v>
+        <v>0.379999780731407</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -54837,19 +53902,19 @@
       </c>
       <c r="B117" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$117)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Revenue])</f>
-        <v>69216.900000000009</v>
+        <v>34492.99</v>
       </c>
       <c r="C117" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$117)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Profit])</f>
-        <v>26302.42</v>
+        <v>13107.330000000002</v>
       </c>
       <c r="D117" s="11">
         <f>SUMPRODUCT((SalesData[Product]=$A$117)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Units])</f>
-        <v>289</v>
+        <v>161</v>
       </c>
       <c r="E117" s="63">
         <f t="shared" si="3"/>
-        <v>0.37999997110532246</v>
+        <v>0.37999982025333273</v>
       </c>
       <c r="F117" s="14"/>
       <c r="G117" s="14"/>
@@ -54874,19 +53939,19 @@
       </c>
       <c r="B118" s="58">
         <f>SUMPRODUCT((SalesData[Product]=$A$118)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Revenue])</f>
-        <v>33856.43</v>
+        <v>26497.75</v>
       </c>
       <c r="C118" s="58">
         <f>SUMPRODUCT((SalesData[Product]=$A$118)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Profit])</f>
-        <v>12865.439999999999</v>
+        <v>10069.15</v>
       </c>
       <c r="D118" s="58">
         <f>SUMPRODUCT((SalesData[Product]=$A$118)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*SalesData[Units])</f>
-        <v>133</v>
+        <v>91</v>
       </c>
       <c r="E118" s="64">
         <f t="shared" si="3"/>
-        <v>0.3799998995759446</v>
+        <v>0.38000018869526658</v>
       </c>
       <c r="F118" s="14"/>
       <c r="G118" s="14"/>
@@ -54911,15 +53976,15 @@
       </c>
       <c r="B119" s="52">
         <f>SUM(B94:B118)</f>
-        <v>4914196.3099999996</v>
+        <v>3304045.19</v>
       </c>
       <c r="C119" s="52">
         <f>SUM(C94:C118)</f>
-        <v>1867394.62</v>
+        <v>1255537.0900000001</v>
       </c>
       <c r="D119" s="52">
         <f>SUM(D94:D118)</f>
-        <v>3831</v>
+        <v>2780</v>
       </c>
       <c r="E119" s="65"/>
       <c r="F119" s="14"/>
@@ -55024,15 +54089,15 @@
       </c>
       <c r="B123" s="67" t="str">
         <f>IF(LARGE($B$94:$B$118,1)&gt;0,IFERROR(INDEX($A$94:$A$118,MATCH(LARGE($B$94:$B$118,1),$B$94:$B$118,0)),""),"")</f>
-        <v>Headset</v>
+        <v>Laptop</v>
       </c>
       <c r="C123" s="35">
         <f>IFERROR(LARGE($B$94:$B$118,1),"")</f>
-        <v>759688.02</v>
+        <v>556108.1</v>
       </c>
       <c r="D123" s="68">
         <f>IFERROR(INDEX($C$94:$C$118,MATCH(LARGE($B$94:$B$118,1),$B$94:$B$118,0)),"")</f>
-        <v>288681.45</v>
+        <v>211321.08</v>
       </c>
       <c r="E123" s="14"/>
       <c r="F123" s="14"/>
@@ -55058,15 +54123,15 @@
       </c>
       <c r="B124" s="70" t="str">
         <f>IF(LARGE($B$94:$B$118,2)&gt;0,IFERROR(INDEX($A$94:$A$118,MATCH(LARGE($B$94:$B$118,2),$B$94:$B$118,0)),""),"")</f>
-        <v>Sofa</v>
+        <v>Floor Lamp</v>
       </c>
       <c r="C124" s="44">
         <f>IFERROR(LARGE($B$94:$B$118,2),"")</f>
-        <v>691271.67</v>
+        <v>477858.96</v>
       </c>
       <c r="D124" s="71">
         <f>IFERROR(INDEX($C$94:$C$118,MATCH(LARGE($B$94:$B$118,2),$B$94:$B$118,0)),"")</f>
-        <v>262683.24</v>
+        <v>181586.38</v>
       </c>
       <c r="E124" s="14"/>
       <c r="F124" s="14"/>
@@ -55092,15 +54157,15 @@
       </c>
       <c r="B125" s="70" t="str">
         <f>IF(LARGE($B$94:$B$118,3)&gt;0,IFERROR(INDEX($A$94:$A$118,MATCH(LARGE($B$94:$B$118,3),$B$94:$B$118,0)),""),"")</f>
-        <v>Desk</v>
+        <v>Smartphone</v>
       </c>
       <c r="C125" s="44">
         <f>IFERROR(LARGE($B$94:$B$118,3),"")</f>
-        <v>548078.28</v>
+        <v>381998.4</v>
       </c>
       <c r="D125" s="71">
         <f>IFERROR(INDEX($C$94:$C$118,MATCH(LARGE($B$94:$B$118,3),$B$94:$B$118,0)),"")</f>
-        <v>208269.75</v>
+        <v>145159.38999999998</v>
       </c>
       <c r="E125" s="14"/>
       <c r="F125" s="14"/>
@@ -55126,15 +54191,15 @@
       </c>
       <c r="B126" s="70" t="str">
         <f>IF(LARGE($B$94:$B$118,4)&gt;0,IFERROR(INDEX($A$94:$A$118,MATCH(LARGE($B$94:$B$118,4),$B$94:$B$118,0)),""),"")</f>
-        <v>Smartphone</v>
+        <v>Monitor</v>
       </c>
       <c r="C126" s="44">
         <f>IFERROR(LARGE($B$94:$B$118,4),"")</f>
-        <v>471256.17000000004</v>
+        <v>298699.01</v>
       </c>
       <c r="D126" s="71">
         <f>IFERROR(INDEX($C$94:$C$118,MATCH(LARGE($B$94:$B$118,4),$B$94:$B$118,0)),"")</f>
-        <v>179077.34</v>
+        <v>113505.62</v>
       </c>
       <c r="E126" s="14"/>
       <c r="F126" s="14"/>
@@ -55160,15 +54225,15 @@
       </c>
       <c r="B127" s="70" t="str">
         <f>IF(LARGE($B$94:$B$118,5)&gt;0,IFERROR(INDEX($A$94:$A$118,MATCH(LARGE($B$94:$B$118,5),$B$94:$B$118,0)),""),"")</f>
-        <v>Monitor</v>
+        <v>Desk</v>
       </c>
       <c r="C127" s="44">
         <f>IFERROR(LARGE($B$94:$B$118,5),"")</f>
-        <v>435057.76999999996</v>
+        <v>294378.95</v>
       </c>
       <c r="D127" s="71">
         <f>IFERROR(INDEX($C$94:$C$118,MATCH(LARGE($B$94:$B$118,5),$B$94:$B$118,0)),"")</f>
-        <v>165321.95000000001</v>
+        <v>111863.99</v>
       </c>
       <c r="E127" s="14"/>
       <c r="F127" s="14"/>
@@ -55194,15 +54259,15 @@
       </c>
       <c r="B128" s="70" t="str">
         <f>IF(LARGE($B$94:$B$118,6)&gt;0,IFERROR(INDEX($A$94:$A$118,MATCH(LARGE($B$94:$B$118,6),$B$94:$B$118,0)),""),"")</f>
-        <v>Bookshelf</v>
+        <v>Headset</v>
       </c>
       <c r="C128" s="44">
         <f>IFERROR(LARGE($B$94:$B$118,6),"")</f>
-        <v>425258.29000000004</v>
+        <v>281950.75</v>
       </c>
       <c r="D128" s="71">
         <f>IFERROR(INDEX($C$94:$C$118,MATCH(LARGE($B$94:$B$118,6),$B$94:$B$118,0)),"")</f>
-        <v>161598.15000000002</v>
+        <v>107141.28</v>
       </c>
       <c r="E128" s="14"/>
       <c r="F128" s="14"/>
@@ -55228,15 +54293,15 @@
       </c>
       <c r="B129" s="70" t="str">
         <f>IF(LARGE($B$94:$B$118,7)&gt;0,IFERROR(INDEX($A$94:$A$118,MATCH(LARGE($B$94:$B$118,7),$B$94:$B$118,0)),""),"")</f>
-        <v>Tablet</v>
+        <v>Sofa</v>
       </c>
       <c r="C129" s="44">
         <f>IFERROR(LARGE($B$94:$B$118,7),"")</f>
-        <v>411205.34</v>
+        <v>212310.41999999998</v>
       </c>
       <c r="D129" s="71">
         <f>IFERROR(INDEX($C$94:$C$118,MATCH(LARGE($B$94:$B$118,7),$B$94:$B$118,0)),"")</f>
-        <v>156258.02999999997</v>
+        <v>80677.959999999992</v>
       </c>
       <c r="E129" s="14"/>
       <c r="F129" s="14"/>
@@ -55262,15 +54327,15 @@
       </c>
       <c r="B130" s="70" t="str">
         <f>IF(LARGE($B$94:$B$118,8)&gt;0,IFERROR(INDEX($A$94:$A$118,MATCH(LARGE($B$94:$B$118,8),$B$94:$B$118,0)),""),"")</f>
-        <v>Laptop</v>
+        <v>Tablet</v>
       </c>
       <c r="C130" s="44">
         <f>IFERROR(LARGE($B$94:$B$118,8),"")</f>
-        <v>360465.91999999998</v>
+        <v>210989.74</v>
       </c>
       <c r="D130" s="71">
         <f>IFERROR(INDEX($C$94:$C$118,MATCH(LARGE($B$94:$B$118,8),$B$94:$B$118,0)),"")</f>
-        <v>136977.04999999999</v>
+        <v>80176.100000000006</v>
       </c>
       <c r="E130" s="14"/>
       <c r="F130" s="14"/>
@@ -55300,11 +54365,11 @@
       </c>
       <c r="C131" s="44">
         <f>IFERROR(LARGE($B$94:$B$118,9),"")</f>
-        <v>216559.27999999997</v>
+        <v>169379.5</v>
       </c>
       <c r="D131" s="71">
         <f>IFERROR(INDEX($C$94:$C$118,MATCH(LARGE($B$94:$B$118,9),$B$94:$B$118,0)),"")</f>
-        <v>82292.529999999984</v>
+        <v>64364.2</v>
       </c>
       <c r="E131" s="14"/>
       <c r="F131" s="14"/>
@@ -55330,15 +54395,15 @@
       </c>
       <c r="B132" s="73" t="str">
         <f>IF(LARGE($B$94:$B$118,10)&gt;0,IFERROR(INDEX($A$94:$A$118,MATCH(LARGE($B$94:$B$118,10),$B$94:$B$118,0)),""),"")</f>
-        <v>Floor Lamp</v>
+        <v>Sweater</v>
       </c>
       <c r="C132" s="74">
         <f>IFERROR(LARGE($B$94:$B$118,10),"")</f>
-        <v>123282.81</v>
+        <v>68513.939999999988</v>
       </c>
       <c r="D132" s="75">
         <f>IFERROR(INDEX($C$94:$C$118,MATCH(LARGE($B$94:$B$118,10),$B$94:$B$118,0)),"")</f>
-        <v>46847.47</v>
+        <v>26035.29</v>
       </c>
       <c r="E132" s="14"/>
       <c r="F132" s="14"/>
@@ -55744,23 +54809,23 @@
       </c>
       <c r="B145" s="11">
         <f>SUMPRODUCT((SalesData[Region]=$A$145)*(SalesData[Category]=$B$144)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])*Dashboard!$AB$2</f>
-        <v>11548.230000000001</v>
+        <v>17883.59</v>
       </c>
       <c r="C145" s="11">
         <f>SUMPRODUCT((SalesData[Region]=$A$145)*(SalesData[Category]=$C$144)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])*Dashboard!$AB$2</f>
-        <v>300225.34999999998</v>
+        <v>443244.79999999999</v>
       </c>
       <c r="D145" s="11">
         <f>SUMPRODUCT((SalesData[Region]=$A$145)*(SalesData[Category]=$D$144)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])*Dashboard!$AB$2</f>
-        <v>23601.149999999998</v>
+        <v>31901.940000000002</v>
       </c>
       <c r="E145" s="11">
         <f>SUMPRODUCT((SalesData[Region]=$A$145)*(SalesData[Category]=$E$144)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])*Dashboard!$AB$2</f>
-        <v>25945.65</v>
+        <v>41259.189999999995</v>
       </c>
       <c r="F145" s="45">
         <f>SUMPRODUCT((SalesData[Region]=$A$145)*(SalesData[Category]=$F$144)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])*Dashboard!$AB$2</f>
-        <v>282685.66000000003</v>
+        <v>557061.39</v>
       </c>
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
@@ -55784,23 +54849,23 @@
       </c>
       <c r="B146" s="11">
         <f>SUMPRODUCT((SalesData[Region]=$A$146)*(SalesData[Category]=$B$144)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])*Dashboard!$AB$2</f>
-        <v>8322.2099999999991</v>
+        <v>4171.8999999999996</v>
       </c>
       <c r="C146" s="11">
         <f>SUMPRODUCT((SalesData[Region]=$A$146)*(SalesData[Category]=$C$144)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])*Dashboard!$AB$2</f>
-        <v>541426.62</v>
+        <v>199447.22</v>
       </c>
       <c r="D146" s="11">
         <f>SUMPRODUCT((SalesData[Region]=$A$146)*(SalesData[Category]=$D$144)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])*Dashboard!$AB$2</f>
-        <v>27015.24</v>
+        <v>41869.579999999994</v>
       </c>
       <c r="E146" s="11">
         <f>SUMPRODUCT((SalesData[Region]=$A$146)*(SalesData[Category]=$E$144)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])*Dashboard!$AB$2</f>
-        <v>53664.340000000004</v>
+        <v>7683.1</v>
       </c>
       <c r="F146" s="45">
         <f>SUMPRODUCT((SalesData[Region]=$A$146)*(SalesData[Category]=$F$144)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])*Dashboard!$AB$2</f>
-        <v>802436.52</v>
+        <v>322962.61</v>
       </c>
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
@@ -55824,23 +54889,23 @@
       </c>
       <c r="B147" s="11">
         <f>SUMPRODUCT((SalesData[Region]=$A$147)*(SalesData[Category]=$B$144)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])*Dashboard!$AB$2</f>
-        <v>13736.79</v>
+        <v>3184</v>
       </c>
       <c r="C147" s="11">
         <f>SUMPRODUCT((SalesData[Region]=$A$147)*(SalesData[Category]=$C$144)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])*Dashboard!$AB$2</f>
-        <v>253668.4</v>
+        <v>203533.17</v>
       </c>
       <c r="D147" s="11">
         <f>SUMPRODUCT((SalesData[Region]=$A$147)*(SalesData[Category]=$D$144)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])*Dashboard!$AB$2</f>
-        <v>55857.479999999996</v>
+        <v>30640.91</v>
       </c>
       <c r="E147" s="11">
         <f>SUMPRODUCT((SalesData[Region]=$A$147)*(SalesData[Category]=$E$144)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])*Dashboard!$AB$2</f>
-        <v>39950.910000000003</v>
+        <v>41489.829999999994</v>
       </c>
       <c r="F147" s="45">
         <f>SUMPRODUCT((SalesData[Region]=$A$147)*(SalesData[Category]=$F$144)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])*Dashboard!$AB$2</f>
-        <v>474331.66</v>
+        <v>263414.59999999998</v>
       </c>
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
@@ -55864,23 +54929,23 @@
       </c>
       <c r="B148" s="11">
         <f>SUMPRODUCT((SalesData[Region]=$A$148)*(SalesData[Category]=$B$144)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])*Dashboard!$AB$2</f>
-        <v>27766.53000000001</v>
+        <v>14090.750000000004</v>
       </c>
       <c r="C148" s="11">
         <f>SUMPRODUCT((SalesData[Region]=$A$148)*(SalesData[Category]=$C$144)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])*Dashboard!$AB$2</f>
-        <v>734325.69</v>
+        <v>121890.18</v>
       </c>
       <c r="D148" s="11">
         <f>SUMPRODUCT((SalesData[Region]=$A$148)*(SalesData[Category]=$D$144)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])*Dashboard!$AB$2</f>
-        <v>74263.78</v>
+        <v>41772.910000000003</v>
       </c>
       <c r="E148" s="11">
         <f>SUMPRODUCT((SalesData[Region]=$A$148)*(SalesData[Category]=$E$144)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])*Dashboard!$AB$2</f>
-        <v>21982.550000000003</v>
+        <v>11797.740000000002</v>
       </c>
       <c r="F148" s="45">
         <f>SUMPRODUCT((SalesData[Region]=$A$148)*(SalesData[Category]=$F$144)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])*Dashboard!$AB$2</f>
-        <v>225203.76</v>
+        <v>420482.31999999995</v>
       </c>
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
@@ -55904,23 +54969,23 @@
       </c>
       <c r="B149" s="58">
         <f>SUMPRODUCT((SalesData[Region]=$A$149)*(SalesData[Category]=$B$144)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])*Dashboard!$AB$2</f>
-        <v>22577.9</v>
+        <v>7671.18</v>
       </c>
       <c r="C149" s="58">
         <f>SUMPRODUCT((SalesData[Region]=$A$149)*(SalesData[Category]=$C$144)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])*Dashboard!$AB$2</f>
-        <v>174804.27</v>
+        <v>245592.05</v>
       </c>
       <c r="D149" s="58">
         <f>SUMPRODUCT((SalesData[Region]=$A$149)*(SalesData[Category]=$D$144)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])*Dashboard!$AB$2</f>
-        <v>35852.76</v>
+        <v>37639.079999999994</v>
       </c>
       <c r="E149" s="58">
         <f>SUMPRODUCT((SalesData[Region]=$A$149)*(SalesData[Category]=$E$144)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])*Dashboard!$AB$2</f>
-        <v>29987.24</v>
+        <v>27536.07</v>
       </c>
       <c r="F149" s="60">
         <f>SUMPRODUCT((SalesData[Region]=$A$149)*(SalesData[Category]=$F$144)*(($B$6="All")+(SalesData[Year]=$B$6))*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])*Dashboard!$AB$2</f>
-        <v>653015.62</v>
+        <v>165825.08000000002</v>
       </c>
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
@@ -56044,11 +55109,11 @@
       </c>
       <c r="B154" s="33">
         <f>SUM(B42:B53)</f>
-        <v>4914196.3100000005</v>
+        <v>3304045.19</v>
       </c>
       <c r="C154" s="80">
         <f>SUM(B42:B53)*Dashboard!$AB$2</f>
-        <v>4914196.3100000005</v>
+        <v>3304045.19</v>
       </c>
       <c r="D154" s="14"/>
       <c r="E154" s="14"/>
@@ -56075,11 +55140,11 @@
       </c>
       <c r="B155" s="11">
         <f>SUM(E42:E53)</f>
-        <v>3046801.69</v>
+        <v>2048508.0999999996</v>
       </c>
       <c r="C155" s="82">
         <f>SUM(E42:E53)*Dashboard!$AB$2</f>
-        <v>3046801.69</v>
+        <v>2048508.0999999996</v>
       </c>
       <c r="D155" s="14"/>
       <c r="E155" s="14"/>
@@ -56106,11 +55171,11 @@
       </c>
       <c r="B156" s="11">
         <f>SUM(F42:F53)</f>
-        <v>1867394.6199999999</v>
+        <v>1255537.0900000001</v>
       </c>
       <c r="C156" s="82">
         <f>SUM(F42:F53)*Dashboard!$AB$2</f>
-        <v>1867394.6199999999</v>
+        <v>1255537.0900000001</v>
       </c>
       <c r="D156" s="14"/>
       <c r="E156" s="14"/>
@@ -56168,11 +55233,11 @@
       </c>
       <c r="B158" s="58">
         <f>SUM(B42:B53)*(1+$I$6/100)</f>
-        <v>7862714.0960000008</v>
+        <v>5286472.3040000005</v>
       </c>
       <c r="C158" s="84">
         <f>SUM(B42:B53)*(1+$I$6/100)*Dashboard!$AB$2</f>
-        <v>7862714.0960000008</v>
+        <v>5286472.3040000005</v>
       </c>
       <c r="D158" s="14"/>
       <c r="E158" s="14"/>
@@ -56418,23 +55483,23 @@
       </c>
       <c r="B166" s="89">
         <f>IF($B$6="All",2025,$B$6)</f>
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C166" s="89">
         <f>IF($B$6="All",2022,IF($B$6&lt;=2022,"n/a",$B$6-1))</f>
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D166" s="90">
         <f>SUMPRODUCT((SalesData[Year]=B166)*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])</f>
-        <v>4914196.3100000015</v>
+        <v>3304045.1900000009</v>
       </c>
       <c r="E166" s="90">
         <f>IF(ISNUMBER(C166),SUMPRODUCT((SalesData[Year]=C166)*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue]),"n/a")</f>
-        <v>3304045.1900000009</v>
+        <v>2945037.5700000003</v>
       </c>
       <c r="F166" s="91">
         <f>IF(NOT(ISNUMBER(C166)),"n/a",IFERROR((D166-E166)/E166,"n/a"))</f>
-        <v>0.48732720874196039</v>
+        <v>0.12190256031266879</v>
       </c>
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
@@ -56537,15 +55602,15 @@
       </c>
       <c r="B170" s="67" t="str">
         <f>IF(SMALL($B$94:$B$118,1)&gt;0,IFERROR(INDEX($A$94:$A$118,MATCH(SMALL($B$94:$B$118,1),$B$94:$B$118,0)),""),"")</f>
-        <v>T-Shirt</v>
+        <v>Coffee</v>
       </c>
       <c r="C170" s="92">
         <f>IFERROR(SMALL($B$94:$B$118,1),"")</f>
-        <v>7547.35</v>
+        <v>7452.74</v>
       </c>
       <c r="D170" s="68">
         <f>IFERROR(INDEX($C$94:$C$118,MATCH(SMALL($B$94:$B$118,1),$B$94:$B$118,0)),"")</f>
-        <v>2868</v>
+        <v>2832.04</v>
       </c>
       <c r="E170" s="14"/>
       <c r="F170" s="14"/>
@@ -56571,15 +55636,15 @@
       </c>
       <c r="B171" s="70" t="str">
         <f>IF(SMALL($B$94:$B$118,2)&gt;0,IFERROR(INDEX($A$94:$A$118,MATCH(SMALL($B$94:$B$118,2),$B$94:$B$118,0)),""),"")</f>
-        <v>Rice</v>
+        <v>Cooking Oil</v>
       </c>
       <c r="C171" s="93">
         <f>IFERROR(SMALL($B$94:$B$118,2),"")</f>
-        <v>12560.67</v>
+        <v>7655.5300000000007</v>
       </c>
       <c r="D171" s="71">
         <f>IFERROR(INDEX($C$94:$C$118,MATCH(SMALL($B$94:$B$118,2),$B$94:$B$118,0)),"")</f>
-        <v>4773.05</v>
+        <v>2909.09</v>
       </c>
       <c r="E171" s="14"/>
       <c r="F171" s="14"/>
@@ -56605,15 +55670,15 @@
       </c>
       <c r="B172" s="70" t="str">
         <f>IF(SMALL($B$94:$B$118,3)&gt;0,IFERROR(INDEX($A$94:$A$118,MATCH(SMALL($B$94:$B$118,3),$B$94:$B$118,0)),""),"")</f>
-        <v>Cooking Oil</v>
+        <v>Sugar</v>
       </c>
       <c r="C172" s="93">
         <f>IFERROR(SMALL($B$94:$B$118,3),"")</f>
-        <v>13501.26</v>
+        <v>8217.7199999999993</v>
       </c>
       <c r="D172" s="71">
         <f>IFERROR(INDEX($C$94:$C$118,MATCH(SMALL($B$94:$B$118,3),$B$94:$B$118,0)),"")</f>
-        <v>5130.49</v>
+        <v>3122.7299999999996</v>
       </c>
       <c r="E172" s="14"/>
       <c r="F172" s="14"/>
@@ -56639,15 +55704,15 @@
       </c>
       <c r="B173" s="70" t="str">
         <f>IF(SMALL($B$94:$B$118,4)&gt;0,IFERROR(INDEX($A$94:$A$118,MATCH(SMALL($B$94:$B$118,4),$B$94:$B$118,0)),""),"")</f>
-        <v>Sugar</v>
+        <v>Rice</v>
       </c>
       <c r="C173" s="93">
         <f>IFERROR(SMALL($B$94:$B$118,4),"")</f>
-        <v>16936.25</v>
+        <v>11141.54</v>
       </c>
       <c r="D173" s="71">
         <f>IFERROR(INDEX($C$94:$C$118,MATCH(SMALL($B$94:$B$118,4),$B$94:$B$118,0)),"")</f>
-        <v>6435.7899999999991</v>
+        <v>4233.79</v>
       </c>
       <c r="E173" s="14"/>
       <c r="F173" s="14"/>
@@ -56673,15 +55738,15 @@
       </c>
       <c r="B174" s="73" t="str">
         <f>IF(SMALL($B$94:$B$118,5)&gt;0,IFERROR(INDEX($A$94:$A$118,MATCH(SMALL($B$94:$B$118,5),$B$94:$B$118,0)),""),"")</f>
-        <v>Football</v>
+        <v>Tea</v>
       </c>
       <c r="C174" s="94">
         <f>IFERROR(SMALL($B$94:$B$118,5),"")</f>
-        <v>18173.059999999998</v>
+        <v>12533.89</v>
       </c>
       <c r="D174" s="75">
         <f>IFERROR(INDEX($C$94:$C$118,MATCH(SMALL($B$94:$B$118,5),$B$94:$B$118,0)),"")</f>
-        <v>6905.7599999999993</v>
+        <v>4762.88</v>
       </c>
       <c r="E174" s="14"/>
       <c r="F174" s="14"/>
@@ -56811,15 +55876,15 @@
       </c>
       <c r="B179" s="67" t="str">
         <f>IF(LARGE($C$94:$C$118,1)&gt;0,IFERROR(INDEX($A$94:$A$118,MATCH(LARGE($C$94:$C$118,1),$C$94:$C$118,0)),""),"")</f>
-        <v>Headset</v>
+        <v>Laptop</v>
       </c>
       <c r="C179" s="35">
         <f>IFERROR(LARGE($C$94:$C$118,1),"")</f>
-        <v>288681.45</v>
+        <v>211321.08</v>
       </c>
       <c r="D179" s="33">
         <f>IFERROR(INDEX($B$94:$B$118,MATCH(LARGE($C$94:$C$118,1),$C$94:$C$118,0)),"")</f>
-        <v>759688.02</v>
+        <v>556108.1</v>
       </c>
       <c r="E179" s="62">
         <v>0.38</v>
@@ -56847,15 +55912,15 @@
       </c>
       <c r="B180" s="70" t="str">
         <f>IF(LARGE($C$94:$C$118,2)&gt;0,IFERROR(INDEX($A$94:$A$118,MATCH(LARGE($C$94:$C$118,2),$C$94:$C$118,0)),""),"")</f>
-        <v>Sofa</v>
+        <v>Floor Lamp</v>
       </c>
       <c r="C180" s="44">
         <f>IFERROR(LARGE($C$94:$C$118,2),"")</f>
-        <v>262683.24</v>
+        <v>181586.38</v>
       </c>
       <c r="D180" s="11">
         <f>IFERROR(INDEX($B$94:$B$118,MATCH(LARGE($C$94:$C$118,2),$C$94:$C$118,0)),"")</f>
-        <v>691271.67</v>
+        <v>477858.96</v>
       </c>
       <c r="E180" s="63">
         <v>0.38</v>
@@ -56883,15 +55948,15 @@
       </c>
       <c r="B181" s="70" t="str">
         <f>IF(LARGE($C$94:$C$118,3)&gt;0,IFERROR(INDEX($A$94:$A$118,MATCH(LARGE($C$94:$C$118,3),$C$94:$C$118,0)),""),"")</f>
-        <v>Desk</v>
+        <v>Smartphone</v>
       </c>
       <c r="C181" s="44">
         <f>IFERROR(LARGE($C$94:$C$118,3),"")</f>
-        <v>208269.75</v>
+        <v>145159.38999999998</v>
       </c>
       <c r="D181" s="11">
         <f>IFERROR(INDEX($B$94:$B$118,MATCH(LARGE($C$94:$C$118,3),$C$94:$C$118,0)),"")</f>
-        <v>548078.28</v>
+        <v>381998.4</v>
       </c>
       <c r="E181" s="63">
         <v>0.38</v>
@@ -56919,15 +55984,15 @@
       </c>
       <c r="B182" s="70" t="str">
         <f>IF(LARGE($C$94:$C$118,4)&gt;0,IFERROR(INDEX($A$94:$A$118,MATCH(LARGE($C$94:$C$118,4),$C$94:$C$118,0)),""),"")</f>
-        <v>Smartphone</v>
+        <v>Monitor</v>
       </c>
       <c r="C182" s="44">
         <f>IFERROR(LARGE($C$94:$C$118,4),"")</f>
-        <v>179077.34</v>
+        <v>113505.62</v>
       </c>
       <c r="D182" s="11">
         <f>IFERROR(INDEX($B$94:$B$118,MATCH(LARGE($C$94:$C$118,4),$C$94:$C$118,0)),"")</f>
-        <v>471256.17000000004</v>
+        <v>298699.01</v>
       </c>
       <c r="E182" s="63">
         <v>0.38</v>
@@ -56955,15 +56020,15 @@
       </c>
       <c r="B183" s="73" t="str">
         <f>IF(LARGE($C$94:$C$118,5)&gt;0,IFERROR(INDEX($A$94:$A$118,MATCH(LARGE($C$94:$C$118,5),$C$94:$C$118,0)),""),"")</f>
-        <v>Monitor</v>
+        <v>Desk</v>
       </c>
       <c r="C183" s="74">
         <f>IFERROR(LARGE($C$94:$C$118,5),"")</f>
-        <v>165321.95000000001</v>
+        <v>111863.99</v>
       </c>
       <c r="D183" s="58">
         <f>IFERROR(INDEX($B$94:$B$118,MATCH(LARGE($C$94:$C$118,5),$C$94:$C$118,0)),"")</f>
-        <v>435057.76999999996</v>
+        <v>294378.95</v>
       </c>
       <c r="E183" s="64">
         <v>0.38</v>
@@ -57104,35 +56169,35 @@
     <row r="188" spans="1:21" ht="16.05" customHeight="1">
       <c r="A188" s="95">
         <f>IF(ISNUMBER($B$6),$B$6,2025)</f>
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B188" s="89">
         <f>IF(A188-1&lt;2022,"n/a",A188-1)</f>
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C188" s="90">
         <f>SUMPRODUCT((SalesData[Year]=A188)*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue])</f>
-        <v>4914196.3100000015</v>
+        <v>3304045.1900000009</v>
       </c>
       <c r="D188" s="90">
         <f>IF(ISNUMBER(B188),SUMPRODUCT((SalesData[Year]=B188)*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Revenue]),"n/a")</f>
-        <v>3304045.1900000009</v>
+        <v>2945037.5700000003</v>
       </c>
       <c r="E188" s="96">
         <f>IFERROR((C188-D188)/D188,"n/a")</f>
-        <v>0.48732720874196039</v>
+        <v>0.12190256031266879</v>
       </c>
       <c r="F188" s="90">
         <f>SUMPRODUCT((SalesData[Year]=A188)*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Profit])</f>
-        <v>1867394.6200000017</v>
+        <v>1255537.0900000003</v>
       </c>
       <c r="G188" s="90">
         <f>IF(ISNUMBER(B188),SUMPRODUCT((SalesData[Year]=B188)*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*SalesData[Profit]),"n/a")</f>
-        <v>1255537.0900000003</v>
+        <v>1119114.19</v>
       </c>
       <c r="H188" s="96">
         <f>IFERROR((F188-G188)/G188,"n/a")</f>
-        <v>0.48732732379893395</v>
+        <v>0.12190257367749074</v>
       </c>
       <c r="I188" s="90">
         <f>SUMPRODUCT((SalesData[Year]=A188)*(($C$6="All")+(SalesData[Quarter]=$C$6))*(($D$6="All")+(SalesData[Month]=$D$6))*(($E$6="All")+(SalesData[Region]=$E$6))*(($F$6="All")+(SalesData[Category]=$F$6))*(($G$6="All")+(SalesData[Salesperson]=$G$6))*(($H$6="All")+(SalesData[Product]=$H$6))*((SalesData[Units]&lt;&gt;0)))</f>
@@ -57181,12 +56246,12 @@
       <c r="U189" s="14"/>
     </row>
     <row r="190" spans="1:21" ht="19.95" customHeight="1">
-      <c r="A190" s="111" t="str">
+      <c r="A190" s="208" t="str">
         <f>"REVENUE BY YEAR  (YOY)  -  "&amp;$A$188&amp;"   vs   "&amp;$B$188</f>
-        <v>REVENUE BY YEAR  (YOY)  -  2024   vs   2023</v>
-      </c>
-      <c r="B190" s="110"/>
-      <c r="C190" s="110"/>
+        <v>REVENUE BY YEAR  (YOY)  -  2023   vs   2022</v>
+      </c>
+      <c r="B190" s="209"/>
+      <c r="C190" s="209"/>
       <c r="D190" s="14"/>
       <c r="E190" s="14"/>
       <c r="F190" s="14"/>
@@ -57238,15 +56303,15 @@
     <row r="192" spans="1:21" ht="16.05" customHeight="1">
       <c r="A192" s="98">
         <f>$A$188</f>
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B192" s="44">
         <f>$C$188</f>
-        <v>4914196.3100000015</v>
+        <v>3304045.1900000009</v>
       </c>
       <c r="C192" s="63">
         <f>IF(ISNUMBER($E$188),$E$188,"-")</f>
-        <v>0.48732720874196039</v>
+        <v>0.12190256031266879</v>
       </c>
       <c r="D192" s="14"/>
       <c r="E192" s="14"/>
@@ -57270,11 +56335,11 @@
     <row r="193" spans="1:21" ht="16.05" customHeight="1">
       <c r="A193" s="99">
         <f>$B$188</f>
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B193" s="100">
         <f>$D$188</f>
-        <v>3304045.1900000009</v>
+        <v>2945037.5700000003</v>
       </c>
       <c r="C193" s="101"/>
       <c r="D193" s="14"/>
@@ -57374,17 +56439,17 @@
       <c r="U196" s="14"/>
     </row>
     <row r="197" spans="1:21" ht="16.05" customHeight="1">
-      <c r="A197" s="154" t="s">
+      <c r="A197" s="126" t="s">
         <v>153</v>
       </c>
-      <c r="B197" s="155">
+      <c r="B197" s="127">
         <f>ROUND(SUM(Calc!$C$42:$C$53)/12,0)</f>
         <v>15</v>
       </c>
-      <c r="C197" s="156" t="s">
+      <c r="C197" s="128" t="s">
         <v>154</v>
       </c>
-      <c r="D197" s="157"/>
+      <c r="D197" s="129"/>
       <c r="E197" s="14"/>
       <c r="F197" s="14"/>
       <c r="G197" s="14"/>
@@ -57404,17 +56469,17 @@
       <c r="U197" s="14"/>
     </row>
     <row r="198" spans="1:21" ht="16.05" customHeight="1">
-      <c r="A198" s="158" t="s">
+      <c r="A198" s="130" t="s">
         <v>155</v>
       </c>
-      <c r="B198" s="159">
+      <c r="B198" s="131">
         <f>IFERROR(SUM(Calc!$D$42:$D$53)/SUM(Calc!$C$42:$C$53),0)</f>
-        <v>21.283333333333335</v>
-      </c>
-      <c r="C198" s="160" t="s">
+        <v>15.444444444444445</v>
+      </c>
+      <c r="C198" s="132" t="s">
         <v>156</v>
       </c>
-      <c r="D198" s="157"/>
+      <c r="D198" s="129"/>
       <c r="E198" s="14"/>
       <c r="F198" s="14"/>
       <c r="G198" s="14"/>
@@ -57434,17 +56499,17 @@
       <c r="U198" s="14"/>
     </row>
     <row r="199" spans="1:21" ht="16.05" customHeight="1">
-      <c r="A199" s="158" t="s">
+      <c r="A199" s="130" t="s">
         <v>157</v>
       </c>
-      <c r="B199" s="161">
+      <c r="B199" s="133">
         <f>IFERROR(SUM(Calc!$D$42:$D$53)/COUNTA(Calc!$A$84:$A$89),0)</f>
-        <v>638.5</v>
-      </c>
-      <c r="C199" s="160" t="s">
+        <v>463.33333333333331</v>
+      </c>
+      <c r="C199" s="132" t="s">
         <v>158</v>
       </c>
-      <c r="D199" s="157"/>
+      <c r="D199" s="129"/>
       <c r="E199" s="14"/>
       <c r="F199" s="14"/>
       <c r="G199" s="14"/>
@@ -57464,17 +56529,17 @@
       <c r="U199" s="14"/>
     </row>
     <row r="200" spans="1:21" ht="16.05" customHeight="1">
-      <c r="A200" s="158" t="s">
+      <c r="A200" s="130" t="s">
         <v>159</v>
       </c>
-      <c r="B200" s="161">
+      <c r="B200" s="133">
         <f>IFERROR(SUM(Calc!$C$42:$C$53)/COUNTA(Calc!$A$66:$A$70),0)</f>
         <v>36</v>
       </c>
-      <c r="C200" s="160" t="s">
+      <c r="C200" s="132" t="s">
         <v>160</v>
       </c>
-      <c r="D200" s="157"/>
+      <c r="D200" s="129"/>
       <c r="E200" s="14"/>
       <c r="F200" s="14"/>
       <c r="G200" s="14"/>
@@ -57494,17 +56559,17 @@
       <c r="U200" s="14"/>
     </row>
     <row r="201" spans="1:21" ht="16.05" customHeight="1">
-      <c r="A201" s="158" t="s">
+      <c r="A201" s="130" t="s">
         <v>161</v>
       </c>
-      <c r="B201" s="162" t="str">
+      <c r="B201" s="134" t="str">
         <f>INDEX(Calc!$A$58:$A$61,MATCH(MAX(Calc!$B$58:$B$61),Calc!$B$58:$B$61,0))</f>
-        <v>Q4</v>
-      </c>
-      <c r="C201" s="160" t="s">
+        <v>Q2</v>
+      </c>
+      <c r="C201" s="132" t="s">
         <v>162</v>
       </c>
-      <c r="D201" s="157"/>
+      <c r="D201" s="129"/>
       <c r="E201" s="14"/>
       <c r="F201" s="14"/>
       <c r="G201" s="14"/>
@@ -57524,17 +56589,17 @@
       <c r="U201" s="14"/>
     </row>
     <row r="202" spans="1:21" ht="16.05" customHeight="1">
-      <c r="A202" s="163" t="s">
+      <c r="A202" s="135" t="s">
         <v>163</v>
       </c>
-      <c r="B202" s="164">
+      <c r="B202" s="136">
         <f>MAX(Calc!$B$58:$B$61)</f>
-        <v>1397478.9100000001</v>
-      </c>
-      <c r="C202" s="165" t="s">
+        <v>1032234.4299999998</v>
+      </c>
+      <c r="C202" s="137" t="s">
         <v>164</v>
       </c>
-      <c r="D202" s="157"/>
+      <c r="D202" s="129"/>
       <c r="E202" s="14"/>
       <c r="F202" s="14"/>
       <c r="G202" s="14"/>
